--- a/12_Equity_Finance/instances/public_tesla_2020_offering.xlsx
+++ b/12_Equity_Finance/instances/public_tesla_2020_offering.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
@@ -25,134 +25,87 @@
     <sheet name="RefreshLog" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
-    <definedName name="FS_DOMAIN" hidden="0" function="0" vbProcedure="0">'Institutional Surface'!$C$5</definedName>
-    <definedName name="FS_MATURITY" hidden="0" function="0" vbProcedure="0">'Institutional Surface'!$C$6</definedName>
-    <definedName name="FS_MODEL_ID" hidden="0" function="0" vbProcedure="0">'Institutional Surface'!$C$4</definedName>
+    <definedName name="FS_MODEL_ID">'Institutional Surface'!$C$4</definedName>
+    <definedName name="FS_DOMAIN">'Institutional Surface'!$C$5</definedName>
+    <definedName name="FS_MATURITY">'Institutional Surface'!$C$6</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
-    <numFmt numFmtId="164" formatCode="0.0%;\(0.0%\);\-"/>
-    <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\);\-"/>
-    <numFmt numFmtId="166" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
-    <numFmt numFmtId="167" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="0.0\x"/>
-    <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
+    <numFmt numFmtId="165" formatCode="$#,##0;($#,##0);&quot;-&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.0x"/>
+    <numFmt numFmtId="168" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
+    <numFmt numFmtId="169" formatCode="$#,##0.00;($#,##0.00);&quot;-&quot;"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
-      <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
       <b val="1"/>
       <sz val="16"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="000000FF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <color rgb="FF000000"/>
+      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <color rgb="FF008000"/>
+      <color rgb="00008000"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Cambria"/>
-      <charset val="1"/>
-      <family val="0"/>
+      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="15"/>
-    </font>
-    <font>
-      <name val="Cambria"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Cambria"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
       <i val="1"/>
-      <color rgb="FF808080"/>
+      <color rgb="00808080"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
       <i val="1"/>
-      <color rgb="FF808080"/>
+      <color rgb="00808080"/>
       <sz val="8"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <color rgb="000000FF"/>
-      <sz val="10"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="8">
@@ -164,32 +117,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF17365D"/>
-        <bgColor rgb="FF333333"/>
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAF7"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
-        <bgColor rgb="FF17365D"/>
+        <fgColor rgb="0017365D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
-        <bgColor rgb="FFD9EAF7"/>
+        <fgColor rgb="00D9EAF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -207,435 +158,196 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
       <bottom style="thin">
-        <color rgb="FFB7B7B7"/>
+        <color rgb="00BFBFBF"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
       <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="00B7B7B7"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="general" vertical="bottom"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="96">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="15" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFBFBFBF"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFD9EAF7"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD9D9D9"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FFB7B7B7"/>
-      <rgbColor rgb="FF17365D"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF1F4E78"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -643,287 +355,395 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
+                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:D20"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="46" min="1" max="1"/>
-    <col width="30" customWidth="1" style="46" min="2" max="2"/>
-    <col width="40" customWidth="1" style="46" min="3" max="3"/>
-    <col width="4" customWidth="1" style="46" min="4" max="4"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.7" customHeight="1" s="47">
-      <c r="B2" s="48" t="inlineStr">
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>[ISSUER] — Equity Finance, Dilution, and Capital Structure</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="47">
-      <c r="B4" s="49" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Issuer / security:</t>
         </is>
       </c>
-      <c r="C4" s="50" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>[fill in]</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="47">
-      <c r="B5" s="49" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Coverage started:</t>
         </is>
       </c>
-      <c r="C5" s="50" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>[date]</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="47">
-      <c r="B6" s="49" t="inlineStr">
+    <row r="6">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Last refreshed:</t>
         </is>
       </c>
-      <c r="C6" s="51" t="inlineStr">
+      <c r="C6" s="44" t="inlineStr">
         <is>
           <t>2020-02-14</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="47">
-      <c r="B7" s="49" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Next financing / shareholder date:</t>
         </is>
       </c>
-      <c r="C7" s="50" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>[date]</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="47">
-      <c r="B8" s="49" t="inlineStr">
+    <row r="8">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Refresh cadence:</t>
         </is>
       </c>
-      <c r="C8" s="52" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Weekly</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="47">
-      <c r="B10" s="49" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Thesis (2-3 sentences):</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="47">
-      <c r="B11" s="50" t="inlineStr">
+    <row r="11">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>[fill in]</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="47"/>
-    <row r="13" ht="15" customHeight="1" s="47"/>
-    <row r="14" ht="15" customHeight="1" s="47"/>
-    <row r="16" ht="15" customHeight="1" s="47">
-      <c r="B16" s="49" t="inlineStr">
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="16">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>COLOR LEGEND</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="47">
-      <c r="B17" s="50" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Blue text</t>
         </is>
       </c>
-      <c r="C17" s="52" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Hardcoded input / scenario lever — edit freely</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="47">
-      <c r="B18" s="52" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Black text</t>
         </is>
       </c>
-      <c r="C18" s="52" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Formula — do not overwrite</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="47">
-      <c r="B19" s="53" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Green text</t>
         </is>
       </c>
-      <c r="C19" s="52" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Link to another sheet in this workbook</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="47">
-      <c r="B20" s="54" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Yellow fill</t>
         </is>
       </c>
-      <c r="C20" s="52" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Key assumption — review every refresh</t>
         </is>
@@ -933,2751 +753,2764 @@
   <mergeCells count="1">
     <mergeCell ref="B11:D14"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A2:I20"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="46" min="1" max="1"/>
-    <col width="26" customWidth="1" style="46" min="2" max="2"/>
-    <col width="13" customWidth="1" style="46" min="3" max="9"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.7" customHeight="1" s="47">
-      <c r="B2" s="48" t="inlineStr">
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Income Statement ($mm)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="47">
-      <c r="A4" s="60" t="n"/>
-      <c r="B4" s="60" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr"/>
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Line item</t>
         </is>
       </c>
-      <c r="C4" s="60" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>FY-2A</t>
         </is>
       </c>
-      <c r="D4" s="60" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>FY-1A</t>
         </is>
       </c>
-      <c r="E4" s="60" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>FY0A</t>
         </is>
       </c>
-      <c r="F4" s="60" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>FY1E</t>
         </is>
       </c>
-      <c r="G4" s="60" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>FY2E</t>
         </is>
       </c>
-      <c r="H4" s="60" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>FY3E</t>
         </is>
       </c>
-      <c r="I4" s="60" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>FY4E</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="47">
-      <c r="B5" s="49" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="C5" s="83" t="n"/>
-      <c r="D5" s="83" t="n"/>
-      <c r="E5" s="83" t="n"/>
-      <c r="F5" s="83">
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12">
         <f>E5*(1+Assumptions!C5)</f>
         <v/>
       </c>
-      <c r="G5" s="83">
+      <c r="G5" s="12">
         <f>F5*(1+Assumptions!D5)</f>
         <v/>
       </c>
-      <c r="H5" s="83">
+      <c r="H5" s="12">
         <f>G5*(1+Assumptions!E5)</f>
         <v/>
       </c>
-      <c r="I5" s="83">
+      <c r="I5" s="12">
         <f>H5*(1+Assumptions!F5)</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="47">
-      <c r="B6" s="52" t="inlineStr">
+    <row r="6">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Revenue growth %</t>
         </is>
       </c>
-      <c r="C6" s="84" t="n"/>
-      <c r="D6" s="84">
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13">
         <f>IFERROR(D5/C5-1,"-")</f>
         <v/>
       </c>
-      <c r="E6" s="84">
+      <c r="E6" s="13">
         <f>IFERROR(E5/D5-1,"-")</f>
         <v/>
       </c>
-      <c r="F6" s="84">
+      <c r="F6" s="13">
         <f>IFERROR(F5/E5-1,"-")</f>
         <v/>
       </c>
-      <c r="G6" s="84">
+      <c r="G6" s="13">
         <f>IFERROR(G5/F5-1,"-")</f>
         <v/>
       </c>
-      <c r="H6" s="84">
+      <c r="H6" s="13">
         <f>IFERROR(H5/G5-1,"-")</f>
         <v/>
       </c>
-      <c r="I6" s="84">
+      <c r="I6" s="13">
         <f>IFERROR(I5/H5-1,"-")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="47">
-      <c r="B7" s="52" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>COGS</t>
         </is>
       </c>
-      <c r="C7" s="83" t="n"/>
-      <c r="D7" s="83" t="n"/>
-      <c r="E7" s="83" t="n"/>
-      <c r="F7" s="83">
+      <c r="C7" s="12" t="n"/>
+      <c r="D7" s="12" t="n"/>
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="12">
         <f>F5*(1-Assumptions!C6)</f>
         <v/>
       </c>
-      <c r="G7" s="83">
+      <c r="G7" s="12">
         <f>G5*(1-Assumptions!D6)</f>
         <v/>
       </c>
-      <c r="H7" s="83">
+      <c r="H7" s="12">
         <f>H5*(1-Assumptions!E6)</f>
         <v/>
       </c>
-      <c r="I7" s="83">
+      <c r="I7" s="12">
         <f>I5*(1-Assumptions!F6)</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="47">
-      <c r="B8" s="49" t="inlineStr">
+    <row r="8">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="C8" s="83" t="n"/>
-      <c r="D8" s="83">
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="12">
         <f>D5-D7</f>
         <v/>
       </c>
-      <c r="E8" s="83">
+      <c r="E8" s="12">
         <f>E5-E7</f>
         <v/>
       </c>
-      <c r="F8" s="83">
+      <c r="F8" s="12">
         <f>F5-F7</f>
         <v/>
       </c>
-      <c r="G8" s="83">
+      <c r="G8" s="12">
         <f>G5-G7</f>
         <v/>
       </c>
-      <c r="H8" s="83">
+      <c r="H8" s="12">
         <f>H5-H7</f>
         <v/>
       </c>
-      <c r="I8" s="83">
+      <c r="I8" s="12">
         <f>I5-I7</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="47">
-      <c r="B9" s="52" t="inlineStr">
+    <row r="9">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C9" s="84" t="n"/>
-      <c r="D9" s="84">
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="13">
         <f>IFERROR(D8/D5,"-")</f>
         <v/>
       </c>
-      <c r="E9" s="84">
+      <c r="E9" s="13">
         <f>IFERROR(E8/E5,"-")</f>
         <v/>
       </c>
-      <c r="F9" s="84">
+      <c r="F9" s="13">
         <f>IFERROR(F8/F5,"-")</f>
         <v/>
       </c>
-      <c r="G9" s="84">
+      <c r="G9" s="13">
         <f>IFERROR(G8/G5,"-")</f>
         <v/>
       </c>
-      <c r="H9" s="84">
+      <c r="H9" s="13">
         <f>IFERROR(H8/H5,"-")</f>
         <v/>
       </c>
-      <c r="I9" s="84">
+      <c r="I9" s="13">
         <f>IFERROR(I8/I5,"-")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="47">
-      <c r="B10" s="52" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Opex</t>
         </is>
       </c>
-      <c r="C10" s="83" t="n"/>
-      <c r="D10" s="83" t="n"/>
-      <c r="E10" s="83" t="n"/>
-      <c r="F10" s="83">
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="12">
         <f>F5*Assumptions!C7</f>
         <v/>
       </c>
-      <c r="G10" s="83">
+      <c r="G10" s="12">
         <f>G5*Assumptions!D7</f>
         <v/>
       </c>
-      <c r="H10" s="83">
+      <c r="H10" s="12">
         <f>H5*Assumptions!E7</f>
         <v/>
       </c>
-      <c r="I10" s="83">
+      <c r="I10" s="12">
         <f>I5*Assumptions!F7</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="47">
-      <c r="B11" s="49" t="inlineStr">
+    <row r="11">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C11" s="83" t="n"/>
-      <c r="D11" s="83" t="n"/>
-      <c r="E11" s="83" t="n"/>
-      <c r="F11" s="83">
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="12">
         <f>F8-F10</f>
         <v/>
       </c>
-      <c r="G11" s="83">
+      <c r="G11" s="12">
         <f>G8-G10</f>
         <v/>
       </c>
-      <c r="H11" s="83">
+      <c r="H11" s="12">
         <f>H8-H10</f>
         <v/>
       </c>
-      <c r="I11" s="83">
+      <c r="I11" s="12">
         <f>I8-I10</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="47">
-      <c r="B12" s="52" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>EBITDA margin %</t>
         </is>
       </c>
-      <c r="C12" s="84" t="n"/>
-      <c r="D12" s="84" t="n"/>
-      <c r="E12" s="84" t="n"/>
-      <c r="F12" s="84">
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13">
         <f>IFERROR(F11/F5,"-")</f>
         <v/>
       </c>
-      <c r="G12" s="84">
+      <c r="G12" s="13">
         <f>IFERROR(G11/G5,"-")</f>
         <v/>
       </c>
-      <c r="H12" s="84">
+      <c r="H12" s="13">
         <f>IFERROR(H11/H5,"-")</f>
         <v/>
       </c>
-      <c r="I12" s="84">
+      <c r="I12" s="13">
         <f>IFERROR(I11/I5,"-")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="47">
-      <c r="B13" s="52" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>D&amp;A</t>
         </is>
       </c>
-      <c r="C13" s="83" t="n"/>
-      <c r="D13" s="83" t="n"/>
-      <c r="E13" s="83" t="n"/>
-      <c r="F13" s="83">
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="12">
         <f>F5*Assumptions!C10*Assumptions!C9</f>
         <v/>
       </c>
-      <c r="G13" s="83">
+      <c r="G13" s="12">
         <f>G5*Assumptions!D10*Assumptions!D9</f>
         <v/>
       </c>
-      <c r="H13" s="83">
+      <c r="H13" s="12">
         <f>H5*Assumptions!E10*Assumptions!E9</f>
         <v/>
       </c>
-      <c r="I13" s="83">
+      <c r="I13" s="12">
         <f>I5*Assumptions!F10*Assumptions!F9</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="47">
-      <c r="B14" s="49" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
-      <c r="C14" s="83" t="n"/>
-      <c r="D14" s="83" t="n"/>
-      <c r="E14" s="83" t="n"/>
-      <c r="F14" s="83">
+      <c r="C14" s="12" t="n"/>
+      <c r="D14" s="12" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="12">
         <f>F11-F13</f>
         <v/>
       </c>
-      <c r="G14" s="83">
+      <c r="G14" s="12">
         <f>G11-G13</f>
         <v/>
       </c>
-      <c r="H14" s="83">
+      <c r="H14" s="12">
         <f>H11-H13</f>
         <v/>
       </c>
-      <c r="I14" s="83">
+      <c r="I14" s="12">
         <f>I11-I13</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="47">
-      <c r="B15" s="52" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Interest expense</t>
         </is>
       </c>
-      <c r="C15" s="83" t="n"/>
-      <c r="D15" s="83" t="n"/>
-      <c r="E15" s="83" t="n"/>
-      <c r="F15" s="83">
+      <c r="C15" s="12" t="n"/>
+      <c r="D15" s="12" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="12">
         <f>$E$15</f>
         <v/>
       </c>
-      <c r="G15" s="83">
+      <c r="G15" s="12">
         <f>$E$15</f>
         <v/>
       </c>
-      <c r="H15" s="83">
+      <c r="H15" s="12">
         <f>$E$15</f>
         <v/>
       </c>
-      <c r="I15" s="83">
+      <c r="I15" s="12">
         <f>$E$15</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="47">
-      <c r="B16" s="52" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Pre-tax income</t>
         </is>
       </c>
-      <c r="C16" s="83" t="n"/>
-      <c r="D16" s="83" t="n"/>
-      <c r="E16" s="83" t="n"/>
-      <c r="F16" s="83">
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12">
         <f>F14-F15</f>
         <v/>
       </c>
-      <c r="G16" s="83">
+      <c r="G16" s="12">
         <f>G14-G15</f>
         <v/>
       </c>
-      <c r="H16" s="83">
+      <c r="H16" s="12">
         <f>H14-H15</f>
         <v/>
       </c>
-      <c r="I16" s="83">
+      <c r="I16" s="12">
         <f>I14-I15</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="47">
-      <c r="B17" s="52" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Tax</t>
         </is>
       </c>
-      <c r="C17" s="83" t="n"/>
-      <c r="D17" s="83" t="n"/>
-      <c r="E17" s="83" t="n"/>
-      <c r="F17" s="83">
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="12">
         <f>F16*Assumptions!C8</f>
         <v/>
       </c>
-      <c r="G17" s="83">
+      <c r="G17" s="12">
         <f>G16*Assumptions!D8</f>
         <v/>
       </c>
-      <c r="H17" s="83">
+      <c r="H17" s="12">
         <f>H16*Assumptions!E8</f>
         <v/>
       </c>
-      <c r="I17" s="83">
+      <c r="I17" s="12">
         <f>I16*Assumptions!F8</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="47">
-      <c r="B18" s="49" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Net income</t>
         </is>
       </c>
-      <c r="C18" s="83" t="n"/>
-      <c r="D18" s="83" t="n"/>
-      <c r="E18" s="83" t="n"/>
-      <c r="F18" s="83">
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="12">
         <f>F16-F17</f>
         <v/>
       </c>
-      <c r="G18" s="83">
+      <c r="G18" s="12">
         <f>G16-G17</f>
         <v/>
       </c>
-      <c r="H18" s="83">
+      <c r="H18" s="12">
         <f>H16-H17</f>
         <v/>
       </c>
-      <c r="I18" s="83">
+      <c r="I18" s="12">
         <f>I16-I17</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="47">
-      <c r="B19" s="52" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Diluted shares</t>
         </is>
       </c>
-      <c r="C19" s="83" t="n"/>
-      <c r="D19" s="83" t="n"/>
-      <c r="E19" s="83" t="n"/>
-      <c r="F19" s="83">
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="12">
         <f>Assumptions!C12</f>
         <v/>
       </c>
-      <c r="G19" s="83">
+      <c r="G19" s="12">
         <f>Assumptions!D12</f>
         <v/>
       </c>
-      <c r="H19" s="83">
+      <c r="H19" s="12">
         <f>Assumptions!E12</f>
         <v/>
       </c>
-      <c r="I19" s="83">
+      <c r="I19" s="12">
         <f>Assumptions!F12</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="47">
-      <c r="B20" s="52" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Diluted EPS</t>
         </is>
       </c>
-      <c r="C20" s="83" t="n"/>
-      <c r="D20" s="83" t="n"/>
-      <c r="E20" s="83" t="n"/>
-      <c r="F20" s="83">
+      <c r="C20" s="12" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="12">
         <f>IFERROR(F18/F19,"-")</f>
         <v/>
       </c>
-      <c r="G20" s="83">
+      <c r="G20" s="12">
         <f>IFERROR(G18/G19,"-")</f>
         <v/>
       </c>
-      <c r="H20" s="83">
+      <c r="H20" s="12">
         <f>IFERROR(H18/H19,"-")</f>
         <v/>
       </c>
-      <c r="I20" s="83">
+      <c r="I20" s="12">
         <f>IFERROR(I18/I19,"-")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A2:G19"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="46" min="1" max="1"/>
-    <col width="26" customWidth="1" style="46" min="2" max="2"/>
-    <col width="13" customWidth="1" style="46" min="3" max="7"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.7" customHeight="1" s="47">
-      <c r="B2" s="48" t="inlineStr">
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Balance Sheet ($mm)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="47">
-      <c r="A4" s="60" t="n"/>
-      <c r="B4" s="60" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr"/>
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Line item</t>
         </is>
       </c>
-      <c r="C4" s="60" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>FY-1A</t>
         </is>
       </c>
-      <c r="D4" s="60" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>FY0A</t>
         </is>
       </c>
-      <c r="E4" s="60" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>FY1E</t>
         </is>
       </c>
-      <c r="F4" s="60" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>FY2E</t>
         </is>
       </c>
-      <c r="G4" s="46" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>FY3E</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="47">
-      <c r="B5" s="52" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Cash &amp; equivalents</t>
         </is>
       </c>
-      <c r="C5" s="83" t="n"/>
-      <c r="D5" s="83" t="n"/>
-      <c r="E5" s="83" t="n"/>
-      <c r="F5" s="83" t="n"/>
-      <c r="G5" s="83" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="47">
-      <c r="B6" s="52" t="inlineStr">
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="12" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Accounts receivable</t>
         </is>
       </c>
-      <c r="C6" s="83" t="n"/>
-      <c r="D6" s="83" t="n"/>
-      <c r="E6" s="83" t="n"/>
-      <c r="F6" s="83" t="n"/>
-      <c r="G6" s="83" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="47">
-      <c r="B7" s="52" t="inlineStr">
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="C7" s="83" t="n"/>
-      <c r="D7" s="83" t="n"/>
-      <c r="E7" s="83" t="n"/>
-      <c r="F7" s="83" t="n"/>
-      <c r="G7" s="83" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="47">
-      <c r="B8" s="49" t="inlineStr">
+      <c r="C7" s="12" t="n"/>
+      <c r="D7" s="12" t="n"/>
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="12" t="n"/>
+      <c r="G7" s="12" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Total current assets</t>
         </is>
       </c>
-      <c r="C8" s="83">
+      <c r="C8" s="12">
         <f>C5+C6+C7</f>
         <v/>
       </c>
-      <c r="D8" s="83">
+      <c r="D8" s="12">
         <f>D5+D6+D7</f>
         <v/>
       </c>
-      <c r="E8" s="83">
+      <c r="E8" s="12">
         <f>E5+E6+E7</f>
         <v/>
       </c>
-      <c r="F8" s="83">
+      <c r="F8" s="12">
         <f>F5+F6+F7</f>
         <v/>
       </c>
-      <c r="G8" s="83">
+      <c r="G8" s="12">
         <f>G5+G6+G7</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="47">
-      <c r="B9" s="52" t="inlineStr">
+    <row r="9">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>PP&amp;E net</t>
         </is>
       </c>
-      <c r="C9" s="83" t="n"/>
-      <c r="D9" s="83" t="n"/>
-      <c r="E9" s="83" t="n"/>
-      <c r="F9" s="83" t="n"/>
-      <c r="G9" s="83" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="47">
-      <c r="B10" s="52" t="inlineStr">
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Goodwill &amp; intangibles</t>
         </is>
       </c>
-      <c r="C10" s="83" t="n"/>
-      <c r="D10" s="83" t="n"/>
-      <c r="E10" s="83" t="n"/>
-      <c r="F10" s="83" t="n"/>
-      <c r="G10" s="83" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="47">
-      <c r="B11" s="49" t="inlineStr">
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="12" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Total assets</t>
         </is>
       </c>
-      <c r="C11" s="83">
+      <c r="C11" s="12">
         <f>C8+C9+C10</f>
         <v/>
       </c>
-      <c r="D11" s="83">
+      <c r="D11" s="12">
         <f>D8+D9+D10</f>
         <v/>
       </c>
-      <c r="E11" s="83">
+      <c r="E11" s="12">
         <f>E8+E9+E10</f>
         <v/>
       </c>
-      <c r="F11" s="83">
+      <c r="F11" s="12">
         <f>F8+F9+F10</f>
         <v/>
       </c>
-      <c r="G11" s="83">
+      <c r="G11" s="12">
         <f>G8+G9+G10</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="47">
-      <c r="B12" s="52" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Accounts payable</t>
         </is>
       </c>
-      <c r="C12" s="83" t="n"/>
-      <c r="D12" s="83" t="n"/>
-      <c r="E12" s="83" t="n"/>
-      <c r="F12" s="83" t="n"/>
-      <c r="G12" s="83" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="47">
-      <c r="B13" s="52" t="inlineStr">
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="12" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Debt (current)</t>
         </is>
       </c>
-      <c r="C13" s="83" t="n"/>
-      <c r="D13" s="83" t="n"/>
-      <c r="E13" s="83" t="n"/>
-      <c r="F13" s="83" t="n"/>
-      <c r="G13" s="83" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="47">
-      <c r="B14" s="49" t="inlineStr">
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="12" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Total current liabilities</t>
         </is>
       </c>
-      <c r="C14" s="83">
+      <c r="C14" s="12">
         <f>C12+C13</f>
         <v/>
       </c>
-      <c r="D14" s="83">
+      <c r="D14" s="12">
         <f>D12+D13</f>
         <v/>
       </c>
-      <c r="E14" s="83">
+      <c r="E14" s="12">
         <f>E12+E13</f>
         <v/>
       </c>
-      <c r="F14" s="83">
+      <c r="F14" s="12">
         <f>F12+F13</f>
         <v/>
       </c>
-      <c r="G14" s="83">
+      <c r="G14" s="12">
         <f>G12+G13</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="47">
-      <c r="B15" s="52" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Long-term debt</t>
         </is>
       </c>
-      <c r="C15" s="83" t="n"/>
-      <c r="D15" s="83" t="n"/>
-      <c r="E15" s="83" t="n"/>
-      <c r="F15" s="83" t="n"/>
-      <c r="G15" s="83" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="47">
-      <c r="B16" s="49" t="inlineStr">
+      <c r="C15" s="12" t="n"/>
+      <c r="D15" s="12" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="12" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Total liabilities</t>
         </is>
       </c>
-      <c r="C16" s="83">
+      <c r="C16" s="12">
         <f>C14+C15</f>
         <v/>
       </c>
-      <c r="D16" s="83">
+      <c r="D16" s="12">
         <f>D14+D15</f>
         <v/>
       </c>
-      <c r="E16" s="83">
+      <c r="E16" s="12">
         <f>E14+E15</f>
         <v/>
       </c>
-      <c r="F16" s="83">
+      <c r="F16" s="12">
         <f>F14+F15</f>
         <v/>
       </c>
-      <c r="G16" s="83">
+      <c r="G16" s="12">
         <f>G14+G15</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="47">
-      <c r="B17" s="49" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Total equity</t>
         </is>
       </c>
-      <c r="C17" s="83" t="n"/>
-      <c r="D17" s="83" t="n"/>
-      <c r="E17" s="83" t="n"/>
-      <c r="F17" s="83" t="n"/>
-      <c r="G17" s="83" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="47">
-      <c r="B19" s="77" t="inlineStr">
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="12" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>Balance check (Total assets - Total liabilities - Total equity, should = 0)</t>
         </is>
       </c>
-      <c r="C19" s="70">
+      <c r="C19" s="15">
         <f>C11-C16-C17</f>
         <v/>
       </c>
-      <c r="D19" s="70">
+      <c r="D19" s="15">
         <f>D11-D16-D17</f>
         <v/>
       </c>
-      <c r="E19" s="70">
+      <c r="E19" s="15">
         <f>E11-E16-E17</f>
         <v/>
       </c>
-      <c r="F19" s="70">
+      <c r="F19" s="15">
         <f>F11-F16-F17</f>
         <v/>
       </c>
-      <c r="G19" s="70">
+      <c r="G19" s="15">
         <f>G11-G16-G17</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A2:G13"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="46" min="1" max="1"/>
-    <col width="26" customWidth="1" style="46" min="2" max="2"/>
-    <col width="13" customWidth="1" style="46" min="3" max="7"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.7" customHeight="1" s="47">
-      <c r="B2" s="48" t="inlineStr">
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Cash Flow ($mm)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="47">
-      <c r="A4" s="60" t="n"/>
-      <c r="B4" s="60" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr"/>
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Line item</t>
         </is>
       </c>
-      <c r="C4" s="60" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>FY-1A</t>
         </is>
       </c>
-      <c r="D4" s="60" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>FY0A</t>
         </is>
       </c>
-      <c r="E4" s="60" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>FY1E</t>
         </is>
       </c>
-      <c r="F4" s="60" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>FY2E</t>
         </is>
       </c>
-      <c r="G4" s="46" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>FY3E</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="47">
-      <c r="B5" s="52" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Net income</t>
         </is>
       </c>
-      <c r="C5" s="83" t="n"/>
-      <c r="D5" s="83" t="n"/>
-      <c r="E5" s="85">
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="16">
         <f>IS!F18</f>
         <v/>
       </c>
-      <c r="F5" s="85">
+      <c r="F5" s="16">
         <f>IS!G18</f>
         <v/>
       </c>
-      <c r="G5" s="85">
+      <c r="G5" s="16">
         <f>IS!H18</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="47">
-      <c r="B6" s="52" t="inlineStr">
+    <row r="6">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>+ D&amp;A</t>
         </is>
       </c>
-      <c r="C6" s="83" t="n"/>
-      <c r="D6" s="83" t="n"/>
-      <c r="E6" s="85">
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="16">
         <f>IS!F13</f>
         <v/>
       </c>
-      <c r="F6" s="85">
+      <c r="F6" s="16">
         <f>IS!G13</f>
         <v/>
       </c>
-      <c r="G6" s="85">
+      <c r="G6" s="16">
         <f>IS!H13</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="47">
-      <c r="B7" s="52" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>+/- Change in NWC</t>
         </is>
       </c>
-      <c r="C7" s="83" t="n"/>
-      <c r="D7" s="83" t="n"/>
-      <c r="E7" s="83" t="n"/>
-      <c r="F7" s="83" t="n"/>
-      <c r="G7" s="83" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="47">
-      <c r="B8" s="49" t="inlineStr">
+      <c r="C7" s="12" t="n"/>
+      <c r="D7" s="12" t="n"/>
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="12" t="n"/>
+      <c r="G7" s="12" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Cash flow from operations</t>
         </is>
       </c>
-      <c r="C8" s="83">
+      <c r="C8" s="12">
         <f>C5+C6+C7</f>
         <v/>
       </c>
-      <c r="D8" s="83">
+      <c r="D8" s="12">
         <f>D5+D6+D7</f>
         <v/>
       </c>
-      <c r="E8" s="83">
+      <c r="E8" s="12">
         <f>E5+E6+E7</f>
         <v/>
       </c>
-      <c r="F8" s="83">
+      <c r="F8" s="12">
         <f>F5+F6+F7</f>
         <v/>
       </c>
-      <c r="G8" s="83">
+      <c r="G8" s="12">
         <f>G5+G6+G7</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="47">
-      <c r="B9" s="52" t="inlineStr">
+    <row r="9">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Capex</t>
         </is>
       </c>
-      <c r="C9" s="83" t="n"/>
-      <c r="D9" s="83" t="n"/>
-      <c r="E9" s="83" t="n"/>
-      <c r="F9" s="83" t="n"/>
-      <c r="G9" s="83" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="47">
-      <c r="B10" s="49" t="inlineStr">
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Free cash flow</t>
         </is>
       </c>
-      <c r="C10" s="83">
+      <c r="C10" s="12">
         <f>C8+C9</f>
         <v/>
       </c>
-      <c r="D10" s="83">
+      <c r="D10" s="12">
         <f>D8+D9</f>
         <v/>
       </c>
-      <c r="E10" s="83">
+      <c r="E10" s="12">
         <f>E8+E9</f>
         <v/>
       </c>
-      <c r="F10" s="83">
+      <c r="F10" s="12">
         <f>F8+F9</f>
         <v/>
       </c>
-      <c r="G10" s="83">
+      <c r="G10" s="12">
         <f>G8+G9</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="47">
-      <c r="B11" s="52" t="inlineStr">
+    <row r="11">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Debt issuance/(repayment)</t>
         </is>
       </c>
-      <c r="C11" s="83" t="n"/>
-      <c r="D11" s="83" t="n"/>
-      <c r="E11" s="83" t="n"/>
-      <c r="F11" s="83" t="n"/>
-      <c r="G11" s="83" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="47">
-      <c r="B12" s="52" t="inlineStr">
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="12" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Dividends/buybacks</t>
         </is>
       </c>
-      <c r="C12" s="83" t="n"/>
-      <c r="D12" s="83" t="n"/>
-      <c r="E12" s="83" t="n"/>
-      <c r="F12" s="83" t="n"/>
-      <c r="G12" s="83" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="47">
-      <c r="B13" s="52" t="inlineStr">
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="12" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Net change in cash</t>
         </is>
       </c>
-      <c r="C13" s="83">
+      <c r="C13" s="12">
         <f>C10+C11+C12</f>
         <v/>
       </c>
-      <c r="D13" s="83">
+      <c r="D13" s="12">
         <f>D10+D11+D12</f>
         <v/>
       </c>
-      <c r="E13" s="83">
+      <c r="E13" s="12">
         <f>E10+E11+E12</f>
         <v/>
       </c>
-      <c r="F13" s="83">
+      <c r="F13" s="12">
         <f>F10+F11+F12</f>
         <v/>
       </c>
-      <c r="G13" s="83">
+      <c r="G13" s="12">
         <f>G10+G11+G12</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:I14"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="46" min="1" max="1"/>
-    <col width="26" customWidth="1" style="46" min="2" max="2"/>
-    <col width="13" customWidth="1" style="46" min="3" max="7"/>
-    <col width="4" customWidth="1" style="46" min="8" max="8"/>
-    <col width="22" customWidth="1" style="46" min="9" max="9"/>
-    <col width="14" customWidth="1" style="46" min="10" max="10"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.7" customHeight="1" s="47">
-      <c r="B2" s="48" t="inlineStr">
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>DCF Valuation</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="47">
-      <c r="C4" s="60" t="inlineStr">
+    <row r="4">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>FY1E</t>
         </is>
       </c>
-      <c r="D4" s="60" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>FY2E</t>
         </is>
       </c>
-      <c r="E4" s="60" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>FY3E</t>
         </is>
       </c>
-      <c r="F4" s="60" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>FY4E</t>
         </is>
       </c>
-      <c r="G4" s="60" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>FY5E</t>
         </is>
       </c>
-      <c r="H4" s="49" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Key outputs</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="47">
-      <c r="B5" s="46" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Unlevered FCF</t>
         </is>
       </c>
-      <c r="C5" s="86">
+      <c r="C5" s="17">
         <f>IS!F14*(1-Assumptions!C8)+IS!F13-IS!F5*Assumptions!C10</f>
         <v/>
       </c>
-      <c r="D5" s="86">
+      <c r="D5" s="17">
         <f>IS!G14*(1-Assumptions!D8)+IS!G13-IS!G5*Assumptions!D10</f>
         <v/>
       </c>
-      <c r="E5" s="86">
+      <c r="E5" s="17">
         <f>IS!H14*(1-Assumptions!E8)+IS!H13-IS!H5*Assumptions!E10</f>
         <v/>
       </c>
-      <c r="F5" s="86">
+      <c r="F5" s="17">
         <f>IS!I14*(1-Assumptions!F8)+IS!I13-IS!I5*Assumptions!F10</f>
         <v/>
       </c>
-      <c r="G5" s="86">
+      <c r="G5" s="17">
         <f>F5*(1+Assumptions!G5)</f>
         <v/>
       </c>
-      <c r="H5" s="46" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="I5" s="87" t="n">
+      <c r="I5" s="18" t="n">
         <v>0.1</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="47">
-      <c r="B6" s="46" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="C6" s="88">
+      <c r="C6" s="19">
         <f>1/(1+$I$5)^(1)</f>
         <v/>
       </c>
-      <c r="D6" s="88">
+      <c r="D6" s="19">
         <f>1/(1+$I$5)^(2)</f>
         <v/>
       </c>
-      <c r="E6" s="88">
+      <c r="E6" s="19">
         <f>1/(1+$I$5)^(3)</f>
         <v/>
       </c>
-      <c r="F6" s="88">
+      <c r="F6" s="19">
         <f>1/(1+$I$5)^(4)</f>
         <v/>
       </c>
-      <c r="G6" s="88">
+      <c r="G6" s="19">
         <f>1/(1+$I$5)^(5)</f>
         <v/>
       </c>
-      <c r="H6" s="46" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="I6" s="87" t="n">
+      <c r="I6" s="18" t="n">
         <v>0.025</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="47">
-      <c r="B7" s="46" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>PV of FCF</t>
         </is>
       </c>
-      <c r="C7" s="89">
+      <c r="C7" s="20">
         <f>C5*C6</f>
         <v/>
       </c>
-      <c r="D7" s="89">
+      <c r="D7" s="20">
         <f>D5*D6</f>
         <v/>
       </c>
-      <c r="E7" s="89">
+      <c r="E7" s="20">
         <f>E5*E6</f>
         <v/>
       </c>
-      <c r="F7" s="89">
+      <c r="F7" s="20">
         <f>F5*F6</f>
         <v/>
       </c>
-      <c r="G7" s="89">
+      <c r="G7" s="20">
         <f>G5*G6</f>
         <v/>
       </c>
-      <c r="H7" s="46" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Terminal value</t>
         </is>
       </c>
-      <c r="I7" s="89">
+      <c r="I7" s="20">
         <f>G5*(1+I6)/(I5-I6)</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="47">
-      <c r="H8" s="46" t="inlineStr">
+    <row r="8">
+      <c r="H8" t="inlineStr">
         <is>
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="I8" s="89">
+      <c r="I8" s="20">
         <f>I7*G6</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="47">
-      <c r="H9" s="46" t="inlineStr">
+    <row r="9">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Sum PV of FCF</t>
         </is>
       </c>
-      <c r="I9" s="89">
+      <c r="I9" s="20">
         <f>SUM(C7:G7)</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="47">
-      <c r="H10" s="46" t="inlineStr">
+    <row r="10">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="I10" s="90">
+      <c r="I10" s="21">
         <f>I8+I9</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="47">
-      <c r="H11" s="46" t="inlineStr">
+    <row r="11">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Less: net debt</t>
         </is>
       </c>
-      <c r="I11" s="91" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="47">
-      <c r="H12" s="46" t="inlineStr">
+      <c r="I11" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Equity value</t>
         </is>
       </c>
-      <c r="I12" s="90">
+      <c r="I12" s="21">
         <f>I10-I11</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="47">
-      <c r="H13" s="46" t="inlineStr">
+    <row r="13">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Diluted shares (mm)</t>
         </is>
       </c>
-      <c r="I13" s="91" t="n">
+      <c r="I13" s="22" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="47">
-      <c r="H14" s="46" t="inlineStr">
+    <row r="14">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Implied value/share</t>
         </is>
       </c>
-      <c r="I14" s="90">
+      <c r="I14" s="21">
         <f>I12/I13</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A2:H13"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="46" min="1" max="1"/>
-    <col width="22" customWidth="1" style="46" min="2" max="2"/>
-    <col width="12" customWidth="1" style="46" min="3" max="8"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.7" customHeight="1" s="47">
-      <c r="B2" s="48" t="inlineStr">
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Comparable Companies</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="47">
-      <c r="A4" s="60" t="n"/>
-      <c r="B4" s="60" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr"/>
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C4" s="60" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="D4" s="60" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Mkt Cap</t>
         </is>
       </c>
-      <c r="E4" s="60" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>EV</t>
         </is>
       </c>
-      <c r="F4" s="60" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>EV/Rev</t>
         </is>
       </c>
-      <c r="G4" s="60" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>EV/EBITDA</t>
         </is>
       </c>
-      <c r="H4" s="60" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>P/E</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="47">
-      <c r="B5" s="50" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>[TICKER]</t>
         </is>
       </c>
-      <c r="C5" s="92" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="92" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="92" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="93" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="93" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="93" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="47">
-      <c r="B6" s="50" t="inlineStr">
+      <c r="C5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>[TICKER]</t>
         </is>
       </c>
-      <c r="C6" s="92" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="92" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="92" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="93" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="93" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="93" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="47">
-      <c r="B7" s="50" t="inlineStr">
+      <c r="C6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>[TICKER]</t>
         </is>
       </c>
-      <c r="C7" s="92" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="92" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="92" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="93" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="93" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="93" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="47">
-      <c r="B8" s="50" t="inlineStr">
+      <c r="C7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>[TICKER]</t>
         </is>
       </c>
-      <c r="C8" s="92" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="92" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="92" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="93" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="93" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="93" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="47">
-      <c r="B9" s="50" t="inlineStr">
+      <c r="C8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>[TICKER]</t>
         </is>
       </c>
-      <c r="C9" s="92" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="92" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="92" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="93" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="93" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="93" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="47">
-      <c r="B10" s="50" t="inlineStr">
+      <c r="C9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>[TICKER]</t>
         </is>
       </c>
-      <c r="C10" s="92" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="92" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="92" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="93" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="93" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="93" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="47">
-      <c r="B11" s="50" t="inlineStr">
+      <c r="C10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>[TICKER]</t>
         </is>
       </c>
-      <c r="C11" s="92" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="92" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="92" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="93" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="93" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="93" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="47">
-      <c r="B13" s="49" t="inlineStr">
+      <c r="C11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Median</t>
         </is>
       </c>
-      <c r="C13" s="90">
+      <c r="C13" s="21">
         <f>MEDIAN(C5:C12)</f>
         <v/>
       </c>
-      <c r="D13" s="90">
+      <c r="D13" s="21">
         <f>MEDIAN(D5:D12)</f>
         <v/>
       </c>
-      <c r="E13" s="90">
+      <c r="E13" s="21">
         <f>MEDIAN(E5:E12)</f>
         <v/>
       </c>
-      <c r="F13" s="94">
+      <c r="F13" s="24">
         <f>MEDIAN(F5:F12)</f>
         <v/>
       </c>
-      <c r="G13" s="94">
+      <c r="G13" s="24">
         <f>MEDIAN(G5:G12)</f>
         <v/>
       </c>
-      <c r="H13" s="94">
+      <c r="H13" s="24">
         <f>MEDIAN(H5:H12)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:G9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="46" min="1" max="1"/>
-    <col width="20" customWidth="1" style="46" min="2" max="2"/>
-    <col width="12" customWidth="1" style="46" min="3" max="8"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.7" customHeight="1" s="47">
-      <c r="B2" s="48" t="inlineStr">
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Sensitivity — Implied Value/Share</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="47">
-      <c r="B4" s="76" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>WACC \ Term. growth</t>
         </is>
       </c>
-      <c r="C4" s="95" t="n">
+      <c r="C4" s="26" t="n">
         <v>0.015</v>
       </c>
-      <c r="D4" s="95" t="n">
+      <c r="D4" s="26" t="n">
         <v>0.02</v>
       </c>
-      <c r="E4" s="95" t="n">
+      <c r="E4" s="26" t="n">
         <v>0.025</v>
       </c>
-      <c r="F4" s="95" t="n">
+      <c r="F4" s="26" t="n">
         <v>0.03</v>
       </c>
-      <c r="G4" s="95" t="n">
+      <c r="G4" s="26" t="n">
         <v>0.035</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="47">
-      <c r="B5" s="95" t="n">
+    <row r="5">
+      <c r="B5" s="26" t="n">
         <v>0.08</v>
       </c>
-      <c r="C5" s="77" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="D5" s="77" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="E5" s="77" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="F5" s="77" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="G5" s="77" t="inlineStr">
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="47">
-      <c r="B6" s="95" t="n">
+    <row r="6">
+      <c r="B6" s="26" t="n">
         <v>0.09</v>
       </c>
-      <c r="C6" s="77" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="D6" s="77" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="E6" s="77" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="F6" s="77" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="G6" s="77" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="47">
-      <c r="B7" s="95" t="n">
+    <row r="7">
+      <c r="B7" s="26" t="n">
         <v>0.1</v>
       </c>
-      <c r="C7" s="77" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="D7" s="77" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="E7" s="77" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="F7" s="77" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="G7" s="77" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="47">
-      <c r="B8" s="95" t="n">
+    <row r="8">
+      <c r="B8" s="26" t="n">
         <v>0.11</v>
       </c>
-      <c r="C8" s="77" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="D8" s="77" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="E8" s="77" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="F8" s="77" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="G8" s="77" t="inlineStr">
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="47">
-      <c r="B9" s="95" t="n">
+    <row r="9">
+      <c r="B9" s="26" t="n">
         <v>0.12</v>
       </c>
-      <c r="C9" s="77" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="D9" s="77" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="E9" s="77" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="F9" s="77" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="G9" s="77" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A2:F14"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="46" min="1" max="1"/>
-    <col width="14" customWidth="1" style="46" min="2" max="2"/>
-    <col width="16" customWidth="1" style="46" min="3" max="3"/>
-    <col width="30" customWidth="1" style="46" min="4" max="5"/>
-    <col width="16" customWidth="1" style="46" min="6" max="6"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.7" customHeight="1" s="47">
-      <c r="B2" s="48" t="inlineStr">
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Refresh Log</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="47">
-      <c r="A4" s="60" t="n"/>
-      <c r="B4" s="60" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr"/>
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C4" s="60" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Trigger</t>
         </is>
       </c>
-      <c r="D4" s="60" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>What changed</t>
         </is>
       </c>
-      <c r="E4" s="60" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>Reviewer notes</t>
         </is>
       </c>
-      <c r="F4" s="60" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Next check</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="47">
-      <c r="B5" s="81" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="C5" s="81" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>External historical evidence materialization</t>
         </is>
       </c>
-      <c r="D5" s="81" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>Generated public case equity-public-tesla-2020-offering from canonical release template</t>
         </is>
       </c>
-      <c r="E5" s="81" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t>External historical case; human stakeholder approval remains pending</t>
         </is>
       </c>
-      <c r="F5" s="81" t="inlineStr">
+      <c r="F5" s="27" t="inlineStr">
         <is>
           <t>On source revision, builder change, monitoring breach, or annual review</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="47">
-      <c r="B6" s="81" t="n"/>
-      <c r="C6" s="81" t="n"/>
-      <c r="D6" s="81" t="n"/>
-      <c r="E6" s="81" t="n"/>
-      <c r="F6" s="81" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="47">
-      <c r="B7" s="81" t="n"/>
-      <c r="C7" s="81" t="n"/>
-      <c r="D7" s="81" t="n"/>
-      <c r="E7" s="81" t="n"/>
-      <c r="F7" s="81" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="47">
-      <c r="B8" s="81" t="n"/>
-      <c r="C8" s="81" t="n"/>
-      <c r="D8" s="81" t="n"/>
-      <c r="E8" s="81" t="n"/>
-      <c r="F8" s="81" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="47">
-      <c r="B9" s="81" t="n"/>
-      <c r="C9" s="81" t="n"/>
-      <c r="D9" s="81" t="n"/>
-      <c r="E9" s="81" t="n"/>
-      <c r="F9" s="81" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="47">
-      <c r="B10" s="81" t="n"/>
-      <c r="C10" s="81" t="n"/>
-      <c r="D10" s="81" t="n"/>
-      <c r="E10" s="81" t="n"/>
-      <c r="F10" s="81" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="47">
-      <c r="B11" s="81" t="n"/>
-      <c r="C11" s="81" t="n"/>
-      <c r="D11" s="81" t="n"/>
-      <c r="E11" s="81" t="n"/>
-      <c r="F11" s="81" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="47">
-      <c r="B12" s="81" t="n"/>
-      <c r="C12" s="81" t="n"/>
-      <c r="D12" s="81" t="n"/>
-      <c r="E12" s="81" t="n"/>
-      <c r="F12" s="81" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="47">
-      <c r="B13" s="81" t="n"/>
-      <c r="C13" s="81" t="n"/>
-      <c r="D13" s="81" t="n"/>
-      <c r="E13" s="81" t="n"/>
-      <c r="F13" s="81" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="47">
-      <c r="B14" s="81" t="n"/>
-      <c r="C14" s="81" t="n"/>
-      <c r="D14" s="81" t="n"/>
-      <c r="E14" s="81" t="n"/>
-      <c r="F14" s="81" t="n"/>
+    <row r="6">
+      <c r="B6" s="27" t="n"/>
+      <c r="C6" s="27" t="n"/>
+      <c r="D6" s="27" t="n"/>
+      <c r="E6" s="27" t="n"/>
+      <c r="F6" s="27" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="27" t="n"/>
+      <c r="C7" s="27" t="n"/>
+      <c r="D7" s="27" t="n"/>
+      <c r="E7" s="27" t="n"/>
+      <c r="F7" s="27" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="27" t="n"/>
+      <c r="C8" s="27" t="n"/>
+      <c r="D8" s="27" t="n"/>
+      <c r="E8" s="27" t="n"/>
+      <c r="F8" s="27" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="27" t="n"/>
+      <c r="C9" s="27" t="n"/>
+      <c r="D9" s="27" t="n"/>
+      <c r="E9" s="27" t="n"/>
+      <c r="F9" s="27" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="27" t="n"/>
+      <c r="C10" s="27" t="n"/>
+      <c r="D10" s="27" t="n"/>
+      <c r="E10" s="27" t="n"/>
+      <c r="F10" s="27" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="27" t="n"/>
+      <c r="C11" s="27" t="n"/>
+      <c r="D11" s="27" t="n"/>
+      <c r="E11" s="27" t="n"/>
+      <c r="F11" s="27" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="27" t="n"/>
+      <c r="C12" s="27" t="n"/>
+      <c r="D12" s="27" t="n"/>
+      <c r="E12" s="27" t="n"/>
+      <c r="F12" s="27" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="27" t="n"/>
+      <c r="C13" s="27" t="n"/>
+      <c r="D13" s="27" t="n"/>
+      <c r="E13" s="27" t="n"/>
+      <c r="F13" s="27" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="27" t="n"/>
+      <c r="C14" s="27" t="n"/>
+      <c r="D14" s="27" t="n"/>
+      <c r="E14" s="27" t="n"/>
+      <c r="F14" s="27" t="n"/>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:F63"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" style="46" min="2" max="2"/>
-    <col width="48" customWidth="1" style="46" min="3" max="3"/>
-    <col width="24" customWidth="1" style="46" min="4" max="4"/>
-    <col width="34" customWidth="1" style="46" min="5" max="5"/>
-    <col width="20" customWidth="1" style="46" min="6" max="6"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="2" ht="18.55" customHeight="1" s="47">
-      <c r="B2" s="55" t="inlineStr">
+    <row r="2">
+      <c r="B2" s="39" t="inlineStr">
         <is>
           <t>Equity Finance — Institutional Decision Surface</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="47">
-      <c r="B4" s="56" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="40" t="inlineStr">
         <is>
           <t>Model ID</t>
         </is>
       </c>
-      <c r="C4" s="57" t="inlineStr">
+      <c r="C4" s="41" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="47">
-      <c r="B5" s="56" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="40" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="C5" s="57" t="inlineStr">
+      <c r="C5" s="41" t="inlineStr">
         <is>
           <t>Equity Finance</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="47">
-      <c r="B6" s="56" t="inlineStr">
+    <row r="6">
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>Declared maturity</t>
         </is>
       </c>
-      <c r="C6" s="57" t="inlineStr">
+      <c r="C6" s="41" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="47">
-      <c r="B7" s="56" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>Canonical builder</t>
         </is>
       </c>
-      <c r="C7" s="57" t="inlineStr">
+      <c r="C7" s="41" t="inlineStr">
         <is>
           <t>tools/builders/build_equity_finance_release.py</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="47">
-      <c r="B8" s="56" t="inlineStr">
+    <row r="8">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>Decision arena</t>
         </is>
       </c>
-      <c r="C8" s="57" t="inlineStr">
+      <c r="C8" s="41" t="inlineStr">
         <is>
           <t>issuer board, ECM, shareholders, counsel and exchange</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="47">
-      <c r="B9" s="56" t="inlineStr">
+    <row r="9">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>Committee artifact</t>
         </is>
       </c>
-      <c r="C9" s="57" t="inlineStr">
+      <c r="C9" s="41" t="inlineStr">
         <is>
           <t>capital raise and dilution memo</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="47">
-      <c r="B10" s="56" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>Operating cadence</t>
         </is>
       </c>
-      <c r="C10" s="57" t="inlineStr">
+      <c r="C10" s="41" t="inlineStr">
         <is>
           <t>daily during offering; quarterly cap table</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="47">
-      <c r="B12" s="58" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="42" t="inlineStr">
         <is>
           <t>Key decision outputs</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="47">
-      <c r="B13" s="59" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="43" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C13" s="59" t="inlineStr">
+      <c r="C13" s="43" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D13" s="59" t="inlineStr">
+      <c r="D13" s="43" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E13" s="59" t="inlineStr">
+      <c r="E13" s="43" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F13" s="59" t="inlineStr">
+      <c r="F13" s="43" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="47">
-      <c r="B14" s="46" t="n">
+    <row r="14">
+      <c r="B14" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="46" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>gross and net proceeds</t>
         </is>
       </c>
-      <c r="F14" s="46" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="47">
-      <c r="B15" s="46" t="n">
+    <row r="15">
+      <c r="B15" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="46" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>pro forma ownership and dilution</t>
         </is>
       </c>
-      <c r="F15" s="46" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="47">
-      <c r="B16" s="46" t="n">
+    <row r="16">
+      <c r="B16" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="46" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>rights take-up / backstop need</t>
         </is>
       </c>
-      <c r="F16" s="46" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="47">
-      <c r="B17" s="46" t="n">
+    <row r="17">
+      <c r="B17" t="n">
         <v>4</v>
       </c>
-      <c r="C17" s="46" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>base, downside and break-even outputs</t>
         </is>
       </c>
-      <c r="F17" s="46" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="47">
-      <c r="B18" s="46" t="n">
+    <row r="18">
+      <c r="B18" t="n">
         <v>5</v>
       </c>
-      <c r="C18" s="46" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>liquidity / funding requirement and binding constraint</t>
         </is>
       </c>
-      <c r="F18" s="46" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="47">
-      <c r="B20" s="58" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="42" t="inlineStr">
         <is>
           <t>Insider questions</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="47">
-      <c r="B21" s="59" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="43" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C21" s="59" t="inlineStr">
+      <c r="C21" s="43" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D21" s="59" t="inlineStr">
+      <c r="D21" s="43" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E21" s="59" t="inlineStr">
+      <c r="E21" s="43" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F21" s="59" t="inlineStr">
+      <c r="F21" s="43" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="47">
-      <c r="B22" s="46" t="n">
+    <row r="22">
+      <c r="B22" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="46" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>What is the real free float after locks?</t>
         </is>
       </c>
-      <c r="F22" s="46" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="47">
-      <c r="B23" s="46" t="n">
+    <row r="23">
+      <c r="B23" t="n">
         <v>2</v>
       </c>
-      <c r="C23" s="46" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Who is economically short through hedges?</t>
         </is>
       </c>
-      <c r="F23" s="46" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="47">
-      <c r="B24" s="46" t="n">
+    <row r="24">
+      <c r="B24" t="n">
         <v>3</v>
       </c>
-      <c r="C24" s="46" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>What is the break price after fees?</t>
         </is>
       </c>
-      <c r="F24" s="46" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="47">
-      <c r="B25" s="46" t="n">
+    <row r="25">
+      <c r="B25" t="n">
         <v>4</v>
       </c>
-      <c r="C25" s="46" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Which assumption is owner-approved versus modeler judgement?</t>
         </is>
       </c>
-      <c r="F25" s="46" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="47">
-      <c r="B26" s="46" t="n">
+    <row r="26">
+      <c r="B26" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="46" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>What fails first and who must act?</t>
         </is>
       </c>
-      <c r="F26" s="46" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="47">
-      <c r="B28" s="58" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="42" t="inlineStr">
         <is>
           <t>Scenario families</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="47">
-      <c r="B29" s="59" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="43" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C29" s="59" t="inlineStr">
+      <c r="C29" s="43" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D29" s="59" t="inlineStr">
+      <c r="D29" s="43" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E29" s="59" t="inlineStr">
+      <c r="E29" s="43" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F29" s="59" t="inlineStr">
+      <c r="F29" s="43" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="47">
-      <c r="B30" s="46" t="n">
+    <row r="30">
+      <c r="B30" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="46" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>discount and market break</t>
         </is>
       </c>
-      <c r="F30" s="46" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="47">
-      <c r="B31" s="46" t="n">
+    <row r="31">
+      <c r="B31" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="46" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>rights under-subscription</t>
         </is>
       </c>
-      <c r="F31" s="46" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="47">
-      <c r="B32" s="46" t="n">
+    <row r="32">
+      <c r="B32" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="46" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>convertible dilution</t>
         </is>
       </c>
-      <c r="F32" s="46" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="47">
-      <c r="B33" s="46" t="n">
+    <row r="33">
+      <c r="B33" t="n">
         <v>4</v>
       </c>
-      <c r="C33" s="46" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>data freshness / source failure</t>
         </is>
       </c>
-      <c r="F33" s="46" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="47">
-      <c r="B34" s="46" t="n">
+    <row r="34">
+      <c r="B34" t="n">
         <v>5</v>
       </c>
-      <c r="C34" s="46" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>combined severe-but-plausible downside</t>
         </is>
       </c>
-      <c r="F34" s="46" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="47">
-      <c r="B36" s="58" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="42" t="inlineStr">
         <is>
           <t>Primary diligence documents</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="47">
-      <c r="B37" s="59" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="43" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C37" s="59" t="inlineStr">
+      <c r="C37" s="43" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D37" s="59" t="inlineStr">
+      <c r="D37" s="43" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E37" s="59" t="inlineStr">
+      <c r="E37" s="43" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F37" s="59" t="inlineStr">
+      <c r="F37" s="43" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="47">
-      <c r="B38" s="46" t="n">
+    <row r="38">
+      <c r="B38" t="n">
         <v>1</v>
       </c>
-      <c r="C38" s="46" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>registration statement / prospectus</t>
         </is>
       </c>
-      <c r="F38" s="46" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" s="47">
-      <c r="B39" s="46" t="n">
+    <row r="39">
+      <c r="B39" t="n">
         <v>2</v>
       </c>
-      <c r="C39" s="46" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>underwriting agreement</t>
         </is>
       </c>
-      <c r="F39" s="46" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" s="47">
-      <c r="B40" s="46" t="n">
+    <row r="40">
+      <c r="B40" t="n">
         <v>3</v>
       </c>
-      <c r="C40" s="46" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>shareholder register</t>
         </is>
       </c>
-      <c r="F40" s="46" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" s="47">
-      <c r="B41" s="46" t="n">
+    <row r="41">
+      <c r="B41" t="n">
         <v>4</v>
       </c>
-      <c r="C41" s="46" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>approved model card and assumption register</t>
         </is>
       </c>
-      <c r="F41" s="46" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" s="47">
-      <c r="B42" s="46" t="n">
+    <row r="42">
+      <c r="B42" t="n">
         <v>5</v>
       </c>
-      <c r="C42" s="46" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>independent validation and challenge record</t>
         </is>
       </c>
-      <c r="F42" s="46" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1" s="47">
-      <c r="B44" s="58" t="inlineStr">
+    <row r="44">
+      <c r="B44" s="42" t="inlineStr">
         <is>
           <t>Challenge tests</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1" s="47">
-      <c r="B45" s="59" t="inlineStr">
+    <row r="45">
+      <c r="B45" s="43" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C45" s="59" t="inlineStr">
+      <c r="C45" s="43" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D45" s="59" t="inlineStr">
+      <c r="D45" s="43" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E45" s="59" t="inlineStr">
+      <c r="E45" s="43" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F45" s="59" t="inlineStr">
+      <c r="F45" s="43" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1" s="47">
-      <c r="B46" s="46" t="n">
+    <row r="46">
+      <c r="B46" t="n">
         <v>1</v>
       </c>
-      <c r="C46" s="46" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>proceeds reconcile</t>
         </is>
       </c>
-      <c r="F46" s="46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1" s="47">
-      <c r="B47" s="46" t="n">
+    <row r="47">
+      <c r="B47" t="n">
         <v>2</v>
       </c>
-      <c r="C47" s="46" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>ownership sums to 100%</t>
         </is>
       </c>
-      <c r="F47" s="46" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1" s="47">
-      <c r="B48" s="46" t="n">
+    <row r="48">
+      <c r="B48" t="n">
         <v>3</v>
       </c>
-      <c r="C48" s="46" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>dilution includes options and convertibles</t>
         </is>
       </c>
-      <c r="F48" s="46" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1" s="47">
-      <c r="B49" s="46" t="n">
+    <row r="49">
+      <c r="B49" t="n">
         <v>4</v>
       </c>
-      <c r="C49" s="46" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>source-to-model lineage is reproducible</t>
         </is>
       </c>
-      <c r="F49" s="46" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1" s="47">
-      <c r="B50" s="46" t="n">
+    <row r="50">
+      <c r="B50" t="n">
         <v>5</v>
       </c>
-      <c r="C50" s="46" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>units, signs, dates and legal definitions reconcile</t>
         </is>
       </c>
-      <c r="F50" s="46" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1" s="47">
-      <c r="B52" s="58" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="42" t="inlineStr">
         <is>
           <t>Known failure modes</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="15" customHeight="1" s="47">
-      <c r="B53" s="59" t="inlineStr">
+    <row r="53">
+      <c r="B53" s="43" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C53" s="59" t="inlineStr">
+      <c r="C53" s="43" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D53" s="59" t="inlineStr">
+      <c r="D53" s="43" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E53" s="59" t="inlineStr">
+      <c r="E53" s="43" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F53" s="59" t="inlineStr">
+      <c r="F53" s="43" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="15" customHeight="1" s="47">
-      <c r="B54" s="46" t="n">
+    <row r="54">
+      <c r="B54" t="n">
         <v>1</v>
       </c>
-      <c r="C54" s="46" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>using basic shares for valuation</t>
         </is>
       </c>
-      <c r="F54" s="46" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="15" customHeight="1" s="47">
-      <c r="B55" s="46" t="n">
+    <row r="55">
+      <c r="B55" t="n">
         <v>2</v>
       </c>
-      <c r="C55" s="46" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>ignoring greenshoe and warrants</t>
         </is>
       </c>
-      <c r="F55" s="46" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="15" customHeight="1" s="47">
-      <c r="B56" s="46" t="n">
+    <row r="56">
+      <c r="B56" t="n">
         <v>3</v>
       </c>
-      <c r="C56" s="46" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>treating convertibles as debt or equity in all cases</t>
         </is>
       </c>
-      <c r="F56" s="46" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1" s="47">
-      <c r="B57" s="46" t="n">
+    <row r="57">
+      <c r="B57" t="n">
         <v>4</v>
       </c>
-      <c r="C57" s="46" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>stale vintage presented as current</t>
         </is>
       </c>
-      <c r="F57" s="46" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1" s="47">
-      <c r="B58" s="46" t="n">
+    <row r="58">
+      <c r="B58" t="n">
         <v>5</v>
       </c>
-      <c r="C58" s="46" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>decision output disconnected from a binding constraint</t>
         </is>
       </c>
-      <c r="F58" s="46" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="15" customHeight="1" s="47">
-      <c r="B60" s="58" t="inlineStr">
+    <row r="60">
+      <c r="B60" s="42" t="inlineStr">
         <is>
           <t>Regulatory / methodological anchors</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="15" customHeight="1" s="47">
-      <c r="B61" s="59" t="inlineStr">
+    <row r="61">
+      <c r="B61" s="43" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="C61" s="59" t="inlineStr">
+      <c r="C61" s="43" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="D61" s="59" t="inlineStr">
+      <c r="D61" s="43" t="inlineStr">
         <is>
           <t>Source URL</t>
         </is>
       </c>
-      <c r="E61" s="59" t="inlineStr">
+      <c r="E61" s="43" t="inlineStr">
         <is>
           <t>Applicability</t>
         </is>
       </c>
-      <c r="F61" s="59" t="inlineStr">
+      <c r="F61" s="43" t="inlineStr">
         <is>
           <t>Review note</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="15" customHeight="1" s="47">
-      <c r="B62" s="46" t="inlineStr">
+    <row r="62">
+      <c r="B62" t="inlineStr">
         <is>
           <t>Federal Reserve SR 26-2 Model Risk Management</t>
         </is>
       </c>
-      <c r="C62" s="46" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>governance, validation, change control, monitoring</t>
         </is>
       </c>
-      <c r="D62" s="46" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>https://www.federalreserve.gov/supervisionreg/srletters/SR2602.htm</t>
         </is>
       </c>
-      <c r="E62" s="46" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>Map explicitly</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="15" customHeight="1" s="47">
-      <c r="B63" s="46" t="inlineStr">
+    <row r="63">
+      <c r="B63" t="inlineStr">
         <is>
           <t>SEC Rule 2a-5</t>
         </is>
       </c>
-      <c r="C63" s="46" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>fair-value governance and testing</t>
         </is>
       </c>
-      <c r="D63" s="46" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>https://www.sec.gov/files/rules/final/2020/ic-34128.pdf</t>
         </is>
       </c>
-      <c r="E63" s="46" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Map explicitly</t>
         </is>
@@ -3702,2247 +3535,2064 @@
     <mergeCell ref="B52:F52"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation sqref="F14:F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="F14:F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="F22:F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="F22:F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="F30:F34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="F30:F34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="F38:F42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="F38:F42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="F46:F50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="F46:F50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="F54:F58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="F54:F58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I54"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="B2:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" style="46" min="2" max="2"/>
-    <col width="22" customWidth="1" style="46" min="3" max="3"/>
-    <col width="52" customWidth="1" style="46" min="4" max="4"/>
-    <col width="46" customWidth="1" style="46" min="5" max="5"/>
-    <col width="36" customWidth="1" style="46" min="6" max="6"/>
-    <col width="14" customWidth="1" style="46" min="7" max="7"/>
-    <col width="18" customWidth="1" style="46" min="8" max="8"/>
-    <col width="14" customWidth="1" style="46" min="9" max="9"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="2" ht="18.55" customHeight="1" s="47">
-      <c r="B2" s="55" t="inlineStr">
+    <row r="2">
+      <c r="B2" s="39" t="inlineStr">
         <is>
           <t>Independent Challenge, Override and Closure Log</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="47">
-      <c r="B4" s="59" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="43" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C4" s="59" t="inlineStr">
+      <c r="C4" s="43" t="inlineStr">
         <is>
           <t>Reviewer</t>
         </is>
       </c>
-      <c r="D4" s="59" t="inlineStr">
+      <c r="D4" s="43" t="inlineStr">
         <is>
           <t>Challenge</t>
         </is>
       </c>
-      <c r="E4" s="59" t="inlineStr">
+      <c r="E4" s="43" t="inlineStr">
         <is>
           <t>Owner response</t>
         </is>
       </c>
-      <c r="F4" s="59" t="inlineStr">
+      <c r="F4" s="43" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="G4" s="59" t="inlineStr">
+      <c r="G4" s="43" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="H4" s="59" t="inlineStr">
+      <c r="H4" s="43" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I4" s="59" t="inlineStr">
+      <c r="I4" s="43" t="inlineStr">
         <is>
           <t>Closure</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="47">
-      <c r="D5" s="46" t="inlineStr">
+    <row r="5">
+      <c r="D5" t="inlineStr">
         <is>
           <t>proceeds reconcile</t>
         </is>
       </c>
-      <c r="H5" s="46" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="47">
-      <c r="D6" s="46" t="inlineStr">
+    <row r="6">
+      <c r="D6" t="inlineStr">
         <is>
           <t>ownership sums to 100%</t>
         </is>
       </c>
-      <c r="H6" s="46" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="47">
-      <c r="D7" s="46" t="inlineStr">
+    <row r="7">
+      <c r="D7" t="inlineStr">
         <is>
           <t>dilution includes options and convertibles</t>
         </is>
       </c>
-      <c r="H7" s="46" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="47">
-      <c r="D8" s="46" t="inlineStr">
+    <row r="8">
+      <c r="D8" t="inlineStr">
         <is>
           <t>source-to-model lineage is reproducible</t>
         </is>
       </c>
-      <c r="H8" s="46" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="47">
-      <c r="D9" s="46" t="inlineStr">
+    <row r="9">
+      <c r="D9" t="inlineStr">
         <is>
           <t>units, signs, dates and legal definitions reconcile</t>
         </is>
       </c>
-      <c r="H9" s="46" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="47">
-      <c r="H10" s="46" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="47">
-      <c r="H11" s="46" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="47">
-      <c r="H12" s="46" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="47">
-      <c r="H13" s="46" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="47">
-      <c r="H14" s="46" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="47">
-      <c r="H15" s="46" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="47">
-      <c r="H16" s="46" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="47">
-      <c r="H17" s="46" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="47">
-      <c r="H18" s="46" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="47">
-      <c r="H19" s="46" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="47">
-      <c r="H20" s="46" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="47">
-      <c r="H21" s="46" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="47">
-      <c r="H22" s="46" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="47">
-      <c r="H23" s="46" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="47">
-      <c r="H24" s="46" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="47">
-      <c r="H25" s="46" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="47">
-      <c r="H26" s="46" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="47">
-      <c r="H27" s="46" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="47">
-      <c r="H28" s="46" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="47">
-      <c r="H29" s="46" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="47">
-      <c r="H30" s="46" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="47">
-      <c r="H31" s="46" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="47">
-      <c r="H32" s="46" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="47">
-      <c r="H33" s="46" t="n"/>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="47">
-      <c r="H34" s="46" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="47">
-      <c r="H35" s="46" t="n"/>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="47">
-      <c r="H36" s="46" t="n"/>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="47">
-      <c r="H37" s="46" t="n"/>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="47">
-      <c r="H38" s="46" t="n"/>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="47">
-      <c r="H39" s="46" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="47">
-      <c r="H40" s="46" t="n"/>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="47">
-      <c r="H41" s="46" t="n"/>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="47">
-      <c r="H42" s="46" t="n"/>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="47">
-      <c r="H43" s="46" t="n"/>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="47">
-      <c r="H44" s="46" t="n"/>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="47">
-      <c r="H45" s="46" t="n"/>
-    </row>
-    <row r="46" ht="15" customHeight="1" s="47">
-      <c r="H46" s="46" t="n"/>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="47">
-      <c r="H47" s="46" t="n"/>
-    </row>
-    <row r="48" ht="15" customHeight="1" s="47">
-      <c r="H48" s="46" t="n"/>
-    </row>
-    <row r="49" ht="15" customHeight="1" s="47">
-      <c r="H49" s="46" t="n"/>
-    </row>
-    <row r="50" ht="15" customHeight="1" s="47">
-      <c r="H50" s="46" t="n"/>
-    </row>
-    <row r="51" ht="15" customHeight="1" s="47">
-      <c r="H51" s="46" t="n"/>
-    </row>
-    <row r="52" ht="15" customHeight="1" s="47">
-      <c r="H52" s="46" t="n"/>
-    </row>
-    <row r="53" ht="15" customHeight="1" s="47">
-      <c r="H53" s="46" t="n"/>
-    </row>
-    <row r="54" ht="15" customHeight="1" s="47">
-      <c r="H54" s="46" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:I2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="H5:H54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="H5:H54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"OPEN,IN REVIEW,REMEDIATED,ACCEPTED RISK,CLOSED"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="G5:G54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="G5:G54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"LOW,MEDIUM,HIGH,CRITICAL"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:J40"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="B2:J8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="46" min="2" max="2"/>
-    <col width="18" customWidth="1" style="46" min="3" max="3"/>
-    <col width="42" customWidth="1" style="46" min="4" max="4"/>
-    <col width="24" customWidth="1" style="46" min="5" max="5"/>
-    <col width="18" customWidth="1" style="46" min="6" max="6"/>
-    <col width="22" customWidth="1" style="46" min="7" max="7"/>
-    <col width="42" customWidth="1" style="46" min="8" max="8"/>
-    <col width="30" customWidth="1" style="46" min="9" max="9"/>
-    <col width="15" customWidth="1" style="46" min="10" max="10"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="2" ht="18.55" customHeight="1" s="47">
-      <c r="B2" s="55" t="inlineStr">
+    <row r="2">
+      <c r="B2" s="39" t="inlineStr">
         <is>
           <t>Source, Transformation, Ownership and Refresh Map</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="47">
-      <c r="B4" s="59" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="43" t="inlineStr">
         <is>
           <t>Source class</t>
         </is>
       </c>
-      <c r="C4" s="59" t="inlineStr">
+      <c r="C4" s="43" t="inlineStr">
         <is>
           <t>Cadence</t>
         </is>
       </c>
-      <c r="D4" s="59" t="inlineStr">
+      <c r="D4" s="43" t="inlineStr">
         <is>
           <t>Control</t>
         </is>
       </c>
-      <c r="E4" s="59" t="inlineStr">
+      <c r="E4" s="43" t="inlineStr">
         <is>
           <t>System / provider</t>
         </is>
       </c>
-      <c r="F4" s="59" t="inlineStr">
+      <c r="F4" s="43" t="inlineStr">
         <is>
           <t>As-of</t>
         </is>
       </c>
-      <c r="G4" s="59" t="inlineStr">
+      <c r="G4" s="43" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="H4" s="59" t="inlineStr">
+      <c r="H4" s="43" t="inlineStr">
         <is>
           <t>Transform</t>
         </is>
       </c>
-      <c r="I4" s="59" t="inlineStr">
+      <c r="I4" s="43" t="inlineStr">
         <is>
           <t>Downstream</t>
         </is>
       </c>
-      <c r="J4" s="59" t="inlineStr">
+      <c r="J4" s="43" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="47">
-      <c r="B5" s="46" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>share count</t>
         </is>
       </c>
-      <c r="C5" s="46" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>event-driven</t>
         </is>
       </c>
-      <c r="D5" s="46" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>basic, diluted and treasury-stock reconciliation</t>
         </is>
       </c>
-      <c r="J5" s="46" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>TO MAP</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="47">
-      <c r="B6" s="46" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>market price and volume</t>
         </is>
       </c>
-      <c r="C6" s="46" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="D6" s="46" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>unaffected and VWAP windows</t>
         </is>
       </c>
-      <c r="J6" s="46" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>TO MAP</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="47">
-      <c r="B7" s="46" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>model governance evidence</t>
         </is>
       </c>
-      <c r="C7" s="46" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>per release</t>
         </is>
       </c>
-      <c r="D7" s="46" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>version, reviewer, sign-off and change log</t>
         </is>
       </c>
-      <c r="J7" s="46" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>TO MAP</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="47">
-      <c r="B8" s="46" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>decision-use snapshot</t>
         </is>
       </c>
-      <c r="C8" s="46" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>per decision</t>
         </is>
       </c>
-      <c r="D8" s="46" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>immutable as-of date and source receipt</t>
         </is>
       </c>
-      <c r="J8" s="46" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>TO MAP</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="47">
-      <c r="J9" s="46" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="47">
-      <c r="J10" s="46" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="47">
-      <c r="J11" s="46" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="47">
-      <c r="J12" s="46" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="47">
-      <c r="J13" s="46" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="47">
-      <c r="J14" s="46" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="47">
-      <c r="J15" s="46" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="47">
-      <c r="J16" s="46" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="47">
-      <c r="J17" s="46" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="47">
-      <c r="J18" s="46" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="47">
-      <c r="J19" s="46" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="47">
-      <c r="J20" s="46" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="47">
-      <c r="J21" s="46" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="47">
-      <c r="J22" s="46" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="47">
-      <c r="J23" s="46" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="47">
-      <c r="J24" s="46" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="47">
-      <c r="J25" s="46" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="47">
-      <c r="J26" s="46" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="47">
-      <c r="J27" s="46" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="47">
-      <c r="J28" s="46" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="47">
-      <c r="J29" s="46" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="47">
-      <c r="J30" s="46" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="47">
-      <c r="J31" s="46" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="47">
-      <c r="J32" s="46" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="47">
-      <c r="J33" s="46" t="n"/>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="47">
-      <c r="J34" s="46" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="47">
-      <c r="J35" s="46" t="n"/>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="47">
-      <c r="J36" s="46" t="n"/>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="47">
-      <c r="J37" s="46" t="n"/>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="47">
-      <c r="J38" s="46" t="n"/>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="47">
-      <c r="J39" s="46" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="47">
-      <c r="J40" s="46" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:J2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="J5:J40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="J5:J40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"TO MAP,ACTIVE,STALE,EXCEPTION,RETIRED"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A2:H14"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="46" min="1" max="1"/>
-    <col width="30" customWidth="1" style="46" min="2" max="2"/>
-    <col width="14" customWidth="1" style="46" min="3" max="7"/>
-    <col width="40" customWidth="1" style="46" min="8" max="8"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.7" customHeight="1" s="47">
-      <c r="B2" s="48" t="inlineStr">
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Assumptions</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="47">
-      <c r="A4" s="60" t="n"/>
-      <c r="B4" s="60" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr"/>
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Driver</t>
         </is>
       </c>
-      <c r="C4" s="60" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>FY1</t>
         </is>
       </c>
-      <c r="D4" s="60" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>FY2</t>
         </is>
       </c>
-      <c r="E4" s="60" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>FY3</t>
         </is>
       </c>
-      <c r="F4" s="60" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>FY4</t>
         </is>
       </c>
-      <c r="G4" s="60" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>FY5</t>
         </is>
       </c>
-      <c r="H4" s="60" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>Source / notes</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="47">
-      <c r="B5" s="52" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Revenue growth %</t>
         </is>
       </c>
-      <c r="C5" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="62" t="inlineStr">
+      <c r="C5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t>Source: [10-K/10-Q cite or user estimate]</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="47">
-      <c r="B6" s="52" t="inlineStr">
+    <row r="6">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C6" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="62" t="inlineStr">
+      <c r="C6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>Source: [10-K/10-Q cite or user estimate]</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="47">
-      <c r="B7" s="52" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Opex % of revenue</t>
         </is>
       </c>
-      <c r="C7" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="62" t="inlineStr">
+      <c r="C7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
         <is>
           <t>Source: [10-K/10-Q cite or user estimate]</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="47">
-      <c r="B8" s="52" t="inlineStr">
+    <row r="8">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Tax rate %</t>
         </is>
       </c>
-      <c r="C8" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="62" t="inlineStr">
+      <c r="C8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
         <is>
           <t>Source: [10-K/10-Q cite or user estimate]</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="47">
-      <c r="B9" s="52" t="inlineStr">
+    <row r="9">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>D&amp;A % of capex</t>
         </is>
       </c>
-      <c r="C9" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="62" t="inlineStr">
+      <c r="C9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
         <is>
           <t>Source: [10-K/10-Q cite or user estimate]</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="47">
-      <c r="B10" s="52" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Capex % of revenue</t>
         </is>
       </c>
-      <c r="C10" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="62" t="inlineStr">
+      <c r="C10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
         <is>
           <t>Source: [10-K/10-Q cite or user estimate]</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="47">
-      <c r="B11" s="52" t="inlineStr">
+    <row r="11">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>NWC % of revenue chg</t>
         </is>
       </c>
-      <c r="C11" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="62" t="inlineStr">
+      <c r="C11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
         <is>
           <t>Source: [10-K/10-Q cite or user estimate]</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="47">
-      <c r="B12" s="52" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Shares outstanding (mm)</t>
         </is>
       </c>
-      <c r="C12" s="64">
+      <c r="C12" s="28">
         <f>'Cap Table &amp; Dilution'!E19</f>
         <v/>
       </c>
-      <c r="D12" s="64">
+      <c r="D12" s="28">
         <f>'Cap Table &amp; Dilution'!E19</f>
         <v/>
       </c>
-      <c r="E12" s="64">
+      <c r="E12" s="28">
         <f>'Cap Table &amp; Dilution'!E19</f>
         <v/>
       </c>
-      <c r="F12" s="64">
+      <c r="F12" s="28">
         <f>'Cap Table &amp; Dilution'!E19</f>
         <v/>
       </c>
-      <c r="G12" s="64">
+      <c r="G12" s="28">
         <f>'Cap Table &amp; Dilution'!E19</f>
         <v/>
       </c>
-      <c r="H12" s="62" t="inlineStr">
+      <c r="H12" s="9" t="inlineStr">
         <is>
           <t>Source: [10-K/10-Q cite or user estimate]</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="47">
-      <c r="B13" s="52" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>WACC %</t>
         </is>
       </c>
-      <c r="C13" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="62" t="inlineStr">
+      <c r="C13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
         <is>
           <t>Source: [10-K/10-Q cite or user estimate]</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="47">
-      <c r="B14" s="52" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Terminal growth %</t>
         </is>
       </c>
-      <c r="C14" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="62" t="inlineStr">
+      <c r="C14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>Source: [10-K/10-Q cite or user estimate]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:F27"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="46" min="1" max="1"/>
-    <col width="42" customWidth="1" style="46" min="2" max="2"/>
-    <col width="18" customWidth="1" style="46" min="3" max="5"/>
-    <col width="46" customWidth="1" style="46" min="6" max="6"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.7" customHeight="1" s="47">
-      <c r="B2" s="48" t="inlineStr">
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Fully Diluted Cap Table and Ownership Attribution</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="47">
-      <c r="B3" s="46" t="inlineStr">
+    <row r="3">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Active scenario</t>
         </is>
       </c>
-      <c r="C3" s="65" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="47">
-      <c r="B4" s="60" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="C4" s="60" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="D4" s="60" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Adversarial</t>
         </is>
       </c>
-      <c r="E4" s="60" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F4" s="60" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Owner / interpretation</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="47">
-      <c r="B5" s="46" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Existing common shares</t>
         </is>
       </c>
-      <c r="C5" s="66" t="n">
+      <c r="C5" s="45" t="n">
         <v>179.7</v>
       </c>
-      <c r="D5" s="67" t="n">
+      <c r="D5" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="E5" s="68">
+      <c r="E5" s="31">
         <f>IF($C$3="Adversarial",D5,C5)</f>
         <v/>
       </c>
-      <c r="F5" s="46" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>pre-transaction issued common</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="47">
-      <c r="B6" s="46" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>In-the-money options / RSUs</t>
         </is>
       </c>
-      <c r="C6" s="67" t="n">
+      <c r="C6" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="67" t="n">
+      <c r="D6" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="E6" s="68">
+      <c r="E6" s="31">
         <f>IF($C$3="Adversarial",D6,C6)</f>
         <v/>
       </c>
-      <c r="F6" s="46" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>treasury-stock or approved dilution method</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="47">
-      <c r="B7" s="46" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Primary shares issued</t>
         </is>
       </c>
-      <c r="C7" s="66" t="n">
+      <c r="C7" s="45" t="n">
         <v>2.65</v>
       </c>
-      <c r="D7" s="67" t="n">
+      <c r="D7" s="30" t="n">
         <v>150</v>
       </c>
-      <c r="E7" s="68">
+      <c r="E7" s="31">
         <f>IF($C$3="Adversarial",D7,C7)</f>
         <v/>
       </c>
-      <c r="F7" s="46" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>new-money common issuance</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="47">
-      <c r="B8" s="46" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Rights shares issued</t>
         </is>
       </c>
-      <c r="C8" s="66" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="67" t="n">
+      <c r="C8" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="E8" s="68">
+      <c r="E8" s="31">
         <f>IF($C$3="Adversarial",D8,C8)</f>
         <v/>
       </c>
-      <c r="F8" s="46" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>shares issued under rights offering</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="47">
-      <c r="B9" s="46" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Convertible principal</t>
         </is>
       </c>
-      <c r="C9" s="69" t="n">
+      <c r="C9" s="32" t="n">
         <v>100</v>
       </c>
-      <c r="D9" s="69" t="n">
+      <c r="D9" s="32" t="n">
         <v>500</v>
       </c>
-      <c r="E9" s="70">
+      <c r="E9" s="15">
         <f>IF($C$3="Adversarial",D9,C9)</f>
         <v/>
       </c>
-      <c r="F9" s="46" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>principal subject to conversion</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="47">
-      <c r="B10" s="46" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Conversion price</t>
         </is>
       </c>
-      <c r="C10" s="71" t="n">
+      <c r="C10" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="D10" s="71" t="n">
+      <c r="D10" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="E10" s="72">
+      <c r="E10" s="34">
         <f>IF($C$3="Adversarial",D10,C10)</f>
         <v/>
       </c>
-      <c r="F10" s="46" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>contractual or adjusted conversion price</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="47">
-      <c r="B11" s="46" t="inlineStr">
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Primary issue price</t>
         </is>
       </c>
-      <c r="C11" s="73" t="n">
+      <c r="C11" s="46" t="n">
         <v>767</v>
       </c>
-      <c r="D11" s="71" t="n">
+      <c r="D11" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="72">
+      <c r="E11" s="34">
         <f>IF($C$3="Adversarial",D11,C11)</f>
         <v/>
       </c>
-      <c r="F11" s="46" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>gross primary price per share</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="47">
-      <c r="B12" s="46" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Transaction fees</t>
         </is>
       </c>
-      <c r="C12" s="74" t="n">
+      <c r="C12" s="47" t="n">
         <v>40.6</v>
       </c>
-      <c r="D12" s="69" t="n">
+      <c r="D12" s="32" t="n">
         <v>20</v>
       </c>
-      <c r="E12" s="70">
+      <c r="E12" s="15">
         <f>IF($C$3="Adversarial",D12,C12)</f>
         <v/>
       </c>
-      <c r="F12" s="46" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>underwriting, legal, exchange, and other costs</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="47">
-      <c r="B13" s="46" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Maximum existing-holder dilution</t>
         </is>
       </c>
-      <c r="C13" s="61" t="n">
+      <c r="C13" s="8" t="n">
         <v>0.35</v>
       </c>
-      <c r="D13" s="61" t="n">
+      <c r="D13" s="8" t="n">
         <v>0.35</v>
       </c>
-      <c r="E13" s="75">
+      <c r="E13" s="35">
         <f>IF($C$3="Adversarial",D13,C13)</f>
         <v/>
       </c>
-      <c r="F13" s="46" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>approved decision threshold</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="47">
-      <c r="B14" s="46" t="inlineStr">
+    <row r="14">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Maximum option / RSU overhang</t>
         </is>
       </c>
-      <c r="C14" s="61" t="n">
+      <c r="C14" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="D14" s="61" t="n">
+      <c r="D14" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="E14" s="75">
+      <c r="E14" s="35">
         <f>IF($C$3="Adversarial",D14,C14)</f>
         <v/>
       </c>
-      <c r="F14" s="46" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>options and RSUs / fully diluted shares</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="47">
-      <c r="B17" s="76" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>Derived outputs</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="47">
-      <c r="B18" s="46" t="inlineStr">
+    <row r="18">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Converted shares</t>
         </is>
       </c>
-      <c r="E18" s="68">
+      <c r="C18" s="31">
+        <f>IFERROR(C9/C10,0)</f>
+        <v/>
+      </c>
+      <c r="D18" s="31">
+        <f>IFERROR(D9/D10,0)</f>
+        <v/>
+      </c>
+      <c r="E18" s="31">
         <f>IFERROR(E9/E10,0)</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="47">
-      <c r="B19" s="46" t="inlineStr">
+    <row r="19">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Fully diluted post-money shares</t>
         </is>
       </c>
-      <c r="E19" s="68">
+      <c r="C19" s="31">
+        <f>SUM(C5:C8)+C18</f>
+        <v/>
+      </c>
+      <c r="D19" s="31">
+        <f>SUM(D5:D8)+D18</f>
+        <v/>
+      </c>
+      <c r="E19" s="31">
         <f>SUM(E5:E8)+E18</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="47">
-      <c r="B20" s="46" t="inlineStr">
+    <row r="20">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Existing common ownership</t>
         </is>
       </c>
-      <c r="E20" s="75">
+      <c r="C20" s="35">
+        <f>IFERROR(C5/C19,0)</f>
+        <v/>
+      </c>
+      <c r="D20" s="35">
+        <f>IFERROR(D5/D19,0)</f>
+        <v/>
+      </c>
+      <c r="E20" s="35">
         <f>IFERROR(E5/E19,0)</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="47">
-      <c r="B21" s="46" t="inlineStr">
+    <row r="21">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Existing-holder dilution</t>
         </is>
       </c>
-      <c r="E21" s="75">
+      <c r="C21" s="35">
+        <f>1-C20</f>
+        <v/>
+      </c>
+      <c r="D21" s="35">
+        <f>1-D20</f>
+        <v/>
+      </c>
+      <c r="E21" s="35">
         <f>1-E20</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="47">
-      <c r="B22" s="46" t="inlineStr">
+    <row r="22">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Option / RSU overhang</t>
         </is>
       </c>
-      <c r="E22" s="75">
+      <c r="C22" s="35">
+        <f>IFERROR(C6/C19,0)</f>
+        <v/>
+      </c>
+      <c r="D22" s="35">
+        <f>IFERROR(D6/D19,0)</f>
+        <v/>
+      </c>
+      <c r="E22" s="35">
         <f>IFERROR(E6/E19,0)</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="47">
-      <c r="B23" s="46" t="inlineStr">
+    <row r="23">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Gross primary proceeds</t>
         </is>
       </c>
-      <c r="E23" s="70">
+      <c r="C23" s="15">
+        <f>C7*C11</f>
+        <v/>
+      </c>
+      <c r="D23" s="15">
+        <f>D7*D11</f>
+        <v/>
+      </c>
+      <c r="E23" s="15">
         <f>E7*E11</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="47">
-      <c r="B24" s="46" t="inlineStr">
+    <row r="24">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Net primary proceeds</t>
         </is>
       </c>
-      <c r="E24" s="70">
+      <c r="C24" s="15">
+        <f>C23-C12</f>
+        <v/>
+      </c>
+      <c r="D24" s="15">
+        <f>D23-D12</f>
+        <v/>
+      </c>
+      <c r="E24" s="15">
         <f>E23-E12</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="47">
-      <c r="B25" s="46" t="inlineStr">
+    <row r="25">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Share-conservation residual</t>
         </is>
       </c>
-      <c r="E25" s="68">
+      <c r="C25" s="31">
+        <f>C19-C5-C6-C7-C8-C18</f>
+        <v/>
+      </c>
+      <c r="D25" s="31">
+        <f>D19-D5-D6-D7-D8-D18</f>
+        <v/>
+      </c>
+      <c r="E25" s="31">
         <f>E19-E5-E6-E7-E8-E18</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="47">
-      <c r="B27" s="77" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>The fully diluted denominator must use the security-specific treasury-stock, if-converted, contingently issuable, and anti-dilution conventions approved for the analysis.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:E21"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="46" min="1" max="1"/>
-    <col width="42" customWidth="1" style="46" min="2" max="2"/>
-    <col width="18" customWidth="1" style="46" min="3" max="4"/>
-    <col width="46" customWidth="1" style="46" min="5" max="5"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.7" customHeight="1" s="47">
-      <c r="B2" s="48" t="inlineStr">
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Rights Offering Economics and Holder Choices</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="47">
-      <c r="B4" s="60" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="C4" s="60" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="D4" s="60" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Adversarial</t>
         </is>
       </c>
-      <c r="E4" s="60" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>Interpretation</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="47">
-      <c r="B5" s="46" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Existing shares entitled</t>
         </is>
       </c>
-      <c r="C5" s="68">
+      <c r="C5" s="31">
         <f>'Cap Table &amp; Dilution'!C5</f>
         <v/>
       </c>
-      <c r="D5" s="68">
+      <c r="D5" s="31">
         <f>'Cap Table &amp; Dilution'!D5</f>
         <v/>
       </c>
-      <c r="E5" s="46" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>record-date eligible shares</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="47">
-      <c r="B6" s="46" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Rights shares offered</t>
         </is>
       </c>
-      <c r="C6" s="68">
+      <c r="C6" s="31">
         <f>'Cap Table &amp; Dilution'!C8</f>
         <v/>
       </c>
-      <c r="D6" s="68">
+      <c r="D6" s="31">
         <f>'Cap Table &amp; Dilution'!D8</f>
         <v/>
       </c>
-      <c r="E6" s="46" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>new shares available through rights</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="47">
-      <c r="B7" s="46" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Cum-rights market price</t>
         </is>
       </c>
-      <c r="C7" s="73" t="n">
+      <c r="C7" s="46" t="n">
         <v>767</v>
       </c>
-      <c r="D7" s="71" t="n">
+      <c r="D7" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="E7" s="46" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>unaffected reference price</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="47">
-      <c r="B8" s="46" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Subscription price</t>
         </is>
       </c>
-      <c r="C8" s="73" t="n">
+      <c r="C8" s="46" t="n">
         <v>767</v>
       </c>
-      <c r="D8" s="71" t="n">
+      <c r="D8" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="E8" s="46" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>cash exercise price</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="47">
-      <c r="B9" s="46" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Expected participation</t>
         </is>
       </c>
-      <c r="C9" s="78" t="n">
+      <c r="C9" s="48" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="78" t="n">
+      <c r="D9" s="48" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="46" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>take-up before standby / rump placement</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="47">
-      <c r="B10" s="46" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Standby / backstop fee</t>
         </is>
       </c>
-      <c r="C10" s="78" t="n">
+      <c r="C10" s="48" t="n">
         <v>0.01176</v>
       </c>
-      <c r="D10" s="61" t="n">
+      <c r="D10" s="8" t="n">
         <v>0.08</v>
       </c>
-      <c r="E10" s="46" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>% of underwritten proceeds</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="47">
-      <c r="B13" s="46" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Theoretical ex-rights price</t>
         </is>
       </c>
-      <c r="C13" s="70">
+      <c r="C13" s="15">
         <f>IFERROR((C5*C7+C6*C8)/(C5+C6),0)</f>
         <v/>
       </c>
-      <c r="D13" s="70">
+      <c r="D13" s="15">
         <f>IFERROR((D5*D7+D6*D8)/(D5+D6),0)</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="47">
-      <c r="B14" s="46" t="inlineStr">
+    <row r="14">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Theoretical value per right / existing share</t>
         </is>
       </c>
-      <c r="C14" s="70">
+      <c r="C14" s="15">
         <f>C7-C13</f>
         <v/>
       </c>
-      <c r="D14" s="70">
+      <c r="D14" s="15">
         <f>D7-D13</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="47">
-      <c r="B15" s="46" t="inlineStr">
+    <row r="15">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Subscription discount</t>
         </is>
       </c>
-      <c r="C15" s="75">
+      <c r="C15" s="35">
         <f>IFERROR(1-C8/C7,0)</f>
         <v/>
       </c>
-      <c r="D15" s="75">
+      <c r="D15" s="35">
         <f>IFERROR(1-D8/D7,0)</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="47">
-      <c r="B16" s="46" t="inlineStr">
+    <row r="16">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Expected subscribed shares</t>
         </is>
       </c>
-      <c r="C16" s="68">
+      <c r="C16" s="31">
         <f>C6*C9</f>
         <v/>
       </c>
-      <c r="D16" s="68">
+      <c r="D16" s="31">
         <f>D6*D9</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="47">
-      <c r="B17" s="46" t="inlineStr">
+    <row r="17">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Expected gross proceeds</t>
         </is>
       </c>
-      <c r="C17" s="70">
+      <c r="C17" s="15">
         <f>C16*C8</f>
         <v/>
       </c>
-      <c r="D17" s="70">
+      <c r="D17" s="15">
         <f>D16*D8</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="47">
-      <c r="B18" s="46" t="inlineStr">
+    <row r="18">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Expected standby fee</t>
         </is>
       </c>
-      <c r="C18" s="70">
+      <c r="C18" s="15">
         <f>(C6-C16)*C8*C10</f>
         <v/>
       </c>
-      <c r="D18" s="70">
+      <c r="D18" s="15">
         <f>(D6-D16)*D8*D10</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="47">
-      <c r="B19" s="46" t="inlineStr">
+    <row r="19">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Expected net rights proceeds</t>
         </is>
       </c>
-      <c r="C19" s="70">
+      <c r="C19" s="15">
         <f>C17-C18</f>
         <v/>
       </c>
-      <c r="D19" s="70">
+      <c r="D19" s="15">
         <f>D17-D18</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="47">
-      <c r="B21" s="77" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>TERP is a frictionless reference. Actual value depends on trading, eligibility, taxes, participation, backstop terms, execution leakage, and the use of proceeds.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:E22"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="46" min="1" max="1"/>
-    <col width="42" customWidth="1" style="46" min="2" max="2"/>
-    <col width="18" customWidth="1" style="46" min="3" max="4"/>
-    <col width="46" customWidth="1" style="46" min="5" max="5"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.7" customHeight="1" s="47">
-      <c r="B2" s="48" t="inlineStr">
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Convertible Security Economics and If-Converted Dilution</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="47">
-      <c r="B4" s="60" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="C4" s="60" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="D4" s="60" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Adversarial</t>
         </is>
       </c>
-      <c r="E4" s="60" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>Interpretation</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="47">
-      <c r="B5" s="46" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Principal</t>
         </is>
       </c>
-      <c r="C5" s="70">
+      <c r="C5" s="15">
         <f>'Cap Table &amp; Dilution'!C9</f>
         <v/>
       </c>
-      <c r="D5" s="70">
+      <c r="D5" s="15">
         <f>'Cap Table &amp; Dilution'!D9</f>
         <v/>
       </c>
-      <c r="E5" s="46" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>outstanding principal</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="47">
-      <c r="B6" s="46" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Conversion price</t>
         </is>
       </c>
-      <c r="C6" s="72">
+      <c r="C6" s="34">
         <f>'Cap Table &amp; Dilution'!C10</f>
         <v/>
       </c>
-      <c r="D6" s="72">
+      <c r="D6" s="34">
         <f>'Cap Table &amp; Dilution'!D10</f>
         <v/>
       </c>
-      <c r="E6" s="46" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>post-adjustment conversion price</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="47">
-      <c r="B7" s="46" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C7" s="71" t="n">
+      <c r="C7" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="D7" s="71" t="n">
+      <c r="D7" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="46" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>market reference</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="47">
-      <c r="B8" s="46" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Cash coupon</t>
         </is>
       </c>
-      <c r="C8" s="61" t="n">
+      <c r="C8" s="8" t="n">
         <v>0.04</v>
       </c>
-      <c r="D8" s="61" t="n">
+      <c r="D8" s="8" t="n">
         <v>0.08</v>
       </c>
-      <c r="E8" s="46" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>annual cash interest</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="47">
-      <c r="B9" s="46" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Remaining tenor</t>
         </is>
       </c>
-      <c r="C9" s="79" t="n">
+      <c r="C9" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="79" t="n">
+      <c r="D9" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="46" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>years</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="47">
-      <c r="B10" s="46" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Redemption premium</t>
         </is>
       </c>
-      <c r="C10" s="61" t="n">
+      <c r="C10" s="8" t="n">
         <v>0.05</v>
       </c>
-      <c r="D10" s="61" t="n">
+      <c r="D10" s="8" t="n">
         <v>0.15</v>
       </c>
-      <c r="E10" s="46" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>premium to principal at maturity / redemption</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="47">
-      <c r="B11" s="46" t="inlineStr">
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Anti-dilution adjusted price</t>
         </is>
       </c>
-      <c r="C11" s="71" t="n">
+      <c r="C11" s="33" t="n">
         <v>9.5</v>
       </c>
-      <c r="D11" s="71" t="n">
+      <c r="D11" s="33" t="n">
         <v>3.5</v>
       </c>
-      <c r="E11" s="46" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>approved modeled adjustment</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="47">
-      <c r="B14" s="46" t="inlineStr">
+    <row r="14">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Contractual converted shares</t>
         </is>
       </c>
-      <c r="C14" s="68">
+      <c r="C14" s="31">
         <f>IFERROR(C5/C6,0)</f>
         <v/>
       </c>
-      <c r="D14" s="68">
+      <c r="D14" s="31">
         <f>IFERROR(D5/D6,0)</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="47">
-      <c r="B15" s="46" t="inlineStr">
+    <row r="15">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Anti-dilution adjusted shares</t>
         </is>
       </c>
-      <c r="C15" s="68">
+      <c r="C15" s="31">
         <f>IFERROR(C5/C11,0)</f>
         <v/>
       </c>
-      <c r="D15" s="68">
+      <c r="D15" s="31">
         <f>IFERROR(D5/D11,0)</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="47">
-      <c r="B16" s="46" t="inlineStr">
+    <row r="16">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Conversion value</t>
         </is>
       </c>
-      <c r="C16" s="70">
+      <c r="C16" s="15">
         <f>C14*C7</f>
         <v/>
       </c>
-      <c r="D16" s="70">
+      <c r="D16" s="15">
         <f>D14*D7</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="47">
-      <c r="B17" s="46" t="inlineStr">
+    <row r="17">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Redemption value</t>
         </is>
       </c>
-      <c r="C17" s="70">
+      <c r="C17" s="15">
         <f>C5*(1+C10)</f>
         <v/>
       </c>
-      <c r="D17" s="70">
+      <c r="D17" s="15">
         <f>D5*(1+D10)</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="47">
-      <c r="B18" s="46" t="inlineStr">
+    <row r="18">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Conversion parity</t>
         </is>
       </c>
-      <c r="C18" s="80">
+      <c r="C18" s="37">
         <f>IFERROR(C16/C5,0)</f>
         <v/>
       </c>
-      <c r="D18" s="80">
+      <c r="D18" s="37">
         <f>IFERROR(D16/D5,0)</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="47">
-      <c r="B19" s="46" t="inlineStr">
+    <row r="19">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Incremental anti-dilution shares</t>
         </is>
       </c>
-      <c r="C19" s="68">
+      <c r="C19" s="31">
         <f>C15-C14</f>
         <v/>
       </c>
-      <c r="D19" s="68">
+      <c r="D19" s="31">
         <f>D15-D14</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="47">
-      <c r="B20" s="46" t="inlineStr">
+    <row r="20">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Annual cash coupon</t>
         </is>
       </c>
-      <c r="C20" s="70">
+      <c r="C20" s="15">
         <f>C5*C8</f>
         <v/>
       </c>
-      <c r="D20" s="70">
+      <c r="D20" s="15">
         <f>D5*D8</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="47">
-      <c r="B22" s="77" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>This sheet models if-converted economics, not the full value of optionality. Call features, soft calls, resets, make-wholes, caps, floors, and settlement elections require explicit terms.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:E26"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="46" min="1" max="1"/>
-    <col width="44" customWidth="1" style="46" min="2" max="2"/>
-    <col width="18" customWidth="1" style="46" min="3" max="4"/>
-    <col width="52" customWidth="1" style="46" min="5" max="5"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.7" customHeight="1" s="47">
-      <c r="B2" s="48" t="inlineStr">
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Equity Finance Decision Dashboard and Independent Checks</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="47">
-      <c r="B4" s="60" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Check / decision</t>
         </is>
       </c>
-      <c r="C4" s="60" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="D4" s="60" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E4" s="60" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>Interpretation / action</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="47">
-      <c r="B5" s="46" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Share-conservation residual</t>
         </is>
       </c>
-      <c r="C5" s="68">
+      <c r="C5" s="27">
         <f>'Cap Table &amp; Dilution'!E25</f>
         <v/>
       </c>
-      <c r="D5" s="81">
+      <c r="D5" s="27">
         <f>IF(ABS(C5)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
-      <c r="E5" s="46" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Fully diluted shares must reconcile to every issued and contingently issuable security.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="47">
-      <c r="B6" s="46" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Ownership / dilution identity</t>
         </is>
       </c>
-      <c r="C6" s="81">
+      <c r="C6" s="27">
         <f>'Cap Table &amp; Dilution'!E20+'Cap Table &amp; Dilution'!E21-1</f>
         <v/>
       </c>
-      <c r="D6" s="81">
+      <c r="D6" s="27">
         <f>IF(ABS(C6)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
-      <c r="E6" s="46" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Existing ownership plus dilution must equal one.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="47">
-      <c r="B7" s="46" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Existing-holder dilution</t>
         </is>
       </c>
-      <c r="C7" s="75">
+      <c r="C7" s="27">
         <f>'Cap Table &amp; Dilution'!E21</f>
         <v/>
       </c>
-      <c r="D7" s="81">
+      <c r="D7" s="27">
         <f>IF(C7&lt;='Cap Table &amp; Dilution'!E13,"PASS","BREACH")</f>
         <v/>
       </c>
-      <c r="E7" s="46" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>A financing that exceeds approved dilution requires explicit board and shareholder analysis.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="47">
-      <c r="B8" s="46" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Option / RSU overhang</t>
         </is>
       </c>
-      <c r="C8" s="75">
+      <c r="C8" s="27">
         <f>'Cap Table &amp; Dilution'!E22</f>
         <v/>
       </c>
-      <c r="D8" s="81">
+      <c r="D8" s="27">
         <f>IF(C8&lt;='Cap Table &amp; Dilution'!E14,"PASS","REVIEW")</f>
         <v/>
       </c>
-      <c r="E8" s="46" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Track employee, acquisition, and contingent-equity dilution separately.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="47">
-      <c r="B9" s="46" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Net primary proceeds</t>
         </is>
       </c>
-      <c r="C9" s="70">
+      <c r="C9" s="27">
         <f>'Cap Table &amp; Dilution'!E24</f>
         <v/>
       </c>
-      <c r="D9" s="81">
+      <c r="D9" s="27">
         <f>IF(C9&gt;=0,"PASS","BREACH")</f>
         <v/>
       </c>
-      <c r="E9" s="46" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Fees and discounts may not exceed gross proceeds.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="47">
-      <c r="B10" s="46" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Rights TERP residual</t>
         </is>
       </c>
-      <c r="C10" s="81">
+      <c r="C10" s="27">
         <f>'Rights Offering'!C13-(('Rights Offering'!C5*'Rights Offering'!C7+'Rights Offering'!C6*'Rights Offering'!C8)/('Rights Offering'!C5+'Rights Offering'!C6))</f>
         <v/>
       </c>
-      <c r="D10" s="81">
+      <c r="D10" s="27">
         <f>IF(ABS(C10)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
-      <c r="E10" s="46" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>TERP must reconcile from old and new shares and their respective prices.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="47">
-      <c r="B11" s="46" t="inlineStr">
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Rights value</t>
         </is>
       </c>
-      <c r="C11" s="70">
+      <c r="C11" s="27">
         <f>'Rights Offering'!C14</f>
         <v/>
       </c>
-      <c r="D11" s="81">
+      <c r="D11" s="27">
         <f>IF(C11&gt;=0,"PASS","REVIEW")</f>
         <v/>
       </c>
-      <c r="E11" s="46" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Negative theoretical right value indicates inconsistent market or subscription inputs.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="47">
-      <c r="B12" s="46" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Adversarial rights participation</t>
         </is>
       </c>
-      <c r="C12" s="75">
+      <c r="C12" s="27">
         <f>'Rights Offering'!D9</f>
         <v/>
       </c>
-      <c r="D12" s="81">
-        <f>IF(C12&gt;=0.75,"PASS",IF(C12&gt;=0.5,"REVIEW","BREACH"))</f>
-        <v/>
-      </c>
-      <c r="E12" s="46" t="inlineStr">
+      <c r="D12" s="27">
+        <f>IF(C12&gt;=0.75,"PASS",IF(C12&gt;=0.50,"REVIEW","BREACH"))</f>
+        <v/>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>Low participation creates rump-placement, backstop, execution, and control risk.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="47">
-      <c r="B13" s="46" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Converted-share reconciliation</t>
         </is>
       </c>
-      <c r="C13" s="81">
+      <c r="C13" s="27">
         <f>'Convertible Securities'!C14-'Cap Table &amp; Dilution'!C18</f>
         <v/>
       </c>
-      <c r="D13" s="81">
+      <c r="D13" s="27">
         <f>IF(ABS(C13)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
-      <c r="E13" s="46" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Cap table and convertible schedule must use the same principal and conversion price.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="47">
-      <c r="B14" s="46" t="inlineStr">
+    <row r="14">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Incremental anti-dilution shares</t>
         </is>
       </c>
-      <c r="C14" s="68">
+      <c r="C14" s="27">
         <f>'Convertible Securities'!D19</f>
         <v/>
       </c>
-      <c r="D14" s="81">
+      <c r="D14" s="27">
         <f>IF(C14&lt;=0,"PASS","REVIEW")</f>
         <v/>
       </c>
-      <c r="E14" s="46" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Reset and anti-dilution provisions can materially expand fully diluted shares in downside cases.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="47">
-      <c r="B16" s="49" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Overall model status</t>
         </is>
       </c>
-      <c r="C16" s="82">
+      <c r="C16" s="38">
         <f>IF(COUNTIF(D5:D14,"FAIL")+COUNTIF(D5:D14,"BREACH")&gt;0,"BREACH",IF(COUNTIF(D5:D14,"REVIEW")&gt;0,"REVIEW","PASS"))</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="47">
-      <c r="B18" s="76" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>Primary decision outputs</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="47">
-      <c r="B19" s="46" t="inlineStr">
+    <row r="19">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Fully diluted shares</t>
         </is>
       </c>
-      <c r="C19" s="68">
+      <c r="C19" s="31">
         <f>'Cap Table &amp; Dilution'!E19</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="47">
-      <c r="B20" s="46" t="inlineStr">
+    <row r="20">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Existing-holder dilution</t>
         </is>
       </c>
-      <c r="C20" s="75">
+      <c r="C20" s="35">
         <f>'Cap Table &amp; Dilution'!E21</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="47">
-      <c r="B21" s="46" t="inlineStr">
+    <row r="21">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Net primary proceeds</t>
         </is>
       </c>
-      <c r="C21" s="70">
+      <c r="C21" s="15">
         <f>'Cap Table &amp; Dilution'!E24</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="47">
-      <c r="B22" s="46" t="inlineStr">
+    <row r="22">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Base TERP</t>
         </is>
       </c>
-      <c r="C22" s="72">
+      <c r="C22" s="34">
         <f>'Rights Offering'!C13</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="47">
-      <c r="B23" s="46" t="inlineStr">
+    <row r="23">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Expected net rights proceeds</t>
         </is>
       </c>
-      <c r="C23" s="70">
+      <c r="C23" s="15">
         <f>'Rights Offering'!C19</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="47">
-      <c r="B24" s="46" t="inlineStr">
+    <row r="24">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Contractual converted shares</t>
         </is>
       </c>
-      <c r="C24" s="68">
+      <c r="C24" s="31">
         <f>'Convertible Securities'!C14</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="47">
-      <c r="B25" s="46" t="inlineStr">
+    <row r="25">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Adversarial anti-dilution shares</t>
         </is>
       </c>
-      <c r="C25" s="68">
+      <c r="C25" s="31">
         <f>'Convertible Securities'!D15</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="47">
-      <c r="B26" s="46" t="inlineStr">
+    <row r="26">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Adversarial redemption value</t>
         </is>
       </c>
-      <c r="C26" s="70">
+      <c r="C26" s="15">
         <f>'Convertible Securities'!D17</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/12_Equity_Finance/instances/public_tesla_2020_offering.xlsx
+++ b/12_Equity_Finance/instances/public_tesla_2020_offering.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="331">
   <si>
     <t xml:space="preserve">[ISSUER] — Equity Finance, Dilution, and Capital Structure</t>
   </si>
@@ -48,33 +48,36 @@
     <t xml:space="preserve">Issuer / security:</t>
   </si>
   <si>
+    <t xml:space="preserve">Tesla February 2020 underwritten primary offering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coverage started:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[date]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last refreshed:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-02-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Next financing / shareholder date:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refresh cadence:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weekly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thesis (2-3 sentences):</t>
+  </si>
+  <si>
     <t xml:space="preserve">[fill in]</t>
   </si>
   <si>
-    <t xml:space="preserve">Coverage started:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[date]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Last refreshed:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-02-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Next financing / shareholder date:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Refresh cadence:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weekly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thesis (2-3 sentences):</t>
-  </si>
-  <si>
     <t xml:space="preserve">COLOR LEGEND</t>
   </si>
   <si>
@@ -958,6 +961,9 @@
   </si>
   <si>
     <t xml:space="preserve">Implied value/share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast base (IS!E5)</t>
   </si>
   <si>
     <t xml:space="preserve">Comparable Companies</t>
@@ -1258,11 +1264,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1712,7 +1718,7 @@
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1720,7 +1726,7 @@
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1728,7 +1734,7 @@
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1747,7 +1753,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
@@ -1769,39 +1775,39 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="3" t="s">
-        <v>12</v>
+      <c r="B17" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1833,43 +1839,43 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15"/>
       <c r="B4" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
+        <v>253</v>
+      </c>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
       <c r="F5" s="34" t="n">
         <f aca="false">E5*(1+Assumptions!C5)</f>
         <v>0</v>
@@ -1889,9 +1895,9 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C6" s="35"/>
+        <v>128</v>
+      </c>
+      <c r="C6" s="16"/>
       <c r="D6" s="35" t="str">
         <f aca="false">IFERROR(D5/C5-1,"-")</f>
         <v>-</v>
@@ -1919,11 +1925,11 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
+        <v>254</v>
+      </c>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
       <c r="F7" s="34" t="n">
         <f aca="false">F5*(1-Assumptions!C6)</f>
         <v>0</v>
@@ -1943,9 +1949,9 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="C8" s="34"/>
+        <v>255</v>
+      </c>
+      <c r="C8" s="23"/>
       <c r="D8" s="34" t="n">
         <f aca="false">D5-D7</f>
         <v>0</v>
@@ -1973,9 +1979,9 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C9" s="35"/>
+        <v>130</v>
+      </c>
+      <c r="C9" s="16"/>
       <c r="D9" s="35" t="str">
         <f aca="false">IFERROR(D8/D5,"-")</f>
         <v>-</v>
@@ -2003,11 +2009,11 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
+        <v>256</v>
+      </c>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
       <c r="F10" s="34" t="n">
         <f aca="false">F5*Assumptions!C7</f>
         <v>0</v>
@@ -2027,11 +2033,11 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
+        <v>257</v>
+      </c>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
       <c r="F11" s="34" t="n">
         <f aca="false">F8-F10</f>
         <v>0</v>
@@ -2051,11 +2057,11 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
+        <v>258</v>
+      </c>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
       <c r="F12" s="35" t="str">
         <f aca="false">IFERROR(F11/F5,"-")</f>
         <v>-</v>
@@ -2075,11 +2081,11 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
+        <v>259</v>
+      </c>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
       <c r="F13" s="34" t="n">
         <f aca="false">F5*Assumptions!C10*Assumptions!C9</f>
         <v>0</v>
@@ -2099,11 +2105,11 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
+        <v>260</v>
+      </c>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
       <c r="F14" s="34" t="n">
         <f aca="false">F11-F13</f>
         <v>0</v>
@@ -2123,11 +2129,11 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
+        <v>261</v>
+      </c>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
       <c r="F15" s="34" t="n">
         <f aca="false">$E$15</f>
         <v>0</v>
@@ -2147,11 +2153,11 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
+        <v>262</v>
+      </c>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
       <c r="F16" s="34" t="n">
         <f aca="false">F14-F15</f>
         <v>0</v>
@@ -2171,11 +2177,11 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
+        <v>263</v>
+      </c>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
       <c r="F17" s="34" t="n">
         <f aca="false">F16*Assumptions!C8</f>
         <v>0</v>
@@ -2195,11 +2201,11 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
+        <v>264</v>
+      </c>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
       <c r="F18" s="34" t="n">
         <f aca="false">F16-F17</f>
         <v>0</v>
@@ -2219,11 +2225,11 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
+        <v>265</v>
+      </c>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
       <c r="F19" s="34" t="n">
         <f aca="false">Assumptions!C12</f>
         <v>197.35</v>
@@ -2243,11 +2249,11 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
+        <v>266</v>
+      </c>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
       <c r="F20" s="34" t="n">
         <f aca="false">IFERROR(F18/F19,"-")</f>
         <v>0</v>
@@ -2291,33 +2297,33 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15"/>
       <c r="B4" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C5" s="34"/>
       <c r="D5" s="34"/>
@@ -2327,7 +2333,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C6" s="34"/>
       <c r="D6" s="34"/>
@@ -2337,7 +2343,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C7" s="34"/>
       <c r="D7" s="34"/>
@@ -2347,7 +2353,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C8" s="34" t="n">
         <f aca="false">C5+C6+C7</f>
@@ -2372,7 +2378,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C9" s="34"/>
       <c r="D9" s="34"/>
@@ -2382,7 +2388,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C10" s="34"/>
       <c r="D10" s="34"/>
@@ -2392,7 +2398,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C11" s="34" t="n">
         <f aca="false">C8+C9+C10</f>
@@ -2417,7 +2423,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C12" s="34"/>
       <c r="D12" s="34"/>
@@ -2427,7 +2433,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C13" s="34"/>
       <c r="D13" s="34"/>
@@ -2437,7 +2443,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C14" s="34" t="n">
         <f aca="false">C12+C13</f>
@@ -2462,7 +2468,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C15" s="34"/>
       <c r="D15" s="34"/>
@@ -2472,7 +2478,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C16" s="34" t="n">
         <f aca="false">C14+C15</f>
@@ -2497,7 +2503,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C17" s="34"/>
       <c r="D17" s="34"/>
@@ -2507,7 +2513,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="29" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C19" s="24" t="n">
         <f aca="false">C11-C16-C17</f>
@@ -2556,33 +2562,33 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15"/>
       <c r="B4" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C5" s="34"/>
       <c r="D5" s="34"/>
@@ -2601,7 +2607,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C6" s="34"/>
       <c r="D6" s="34"/>
@@ -2620,7 +2626,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C7" s="34"/>
       <c r="D7" s="34"/>
@@ -2630,7 +2636,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C8" s="34" t="n">
         <f aca="false">C5+C6+C7</f>
@@ -2655,7 +2661,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C9" s="34"/>
       <c r="D9" s="34"/>
@@ -2665,7 +2671,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C10" s="34" t="n">
         <f aca="false">C8+C9</f>
@@ -2690,7 +2696,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C11" s="34"/>
       <c r="D11" s="34"/>
@@ -2700,7 +2706,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C12" s="34"/>
       <c r="D12" s="34"/>
@@ -2710,7 +2716,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C13" s="34" t="n">
         <f aca="false">C10+C11+C12</f>
@@ -2749,7 +2755,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:I14"/>
+  <dimension ref="B2:I15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -2762,32 +2768,32 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C5" s="37" t="n">
         <f aca="false">IS!F14*(1-Assumptions!C8)+IS!F13-IS!F5*Assumptions!C10</f>
@@ -2810,7 +2816,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I5" s="38" t="n">
         <v>0.1</v>
@@ -2818,7 +2824,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C6" s="39" t="n">
         <f aca="false">1/(1+$I$5)^(1)</f>
@@ -2841,7 +2847,7 @@
         <v>0.620921323059155</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="I6" s="38" t="n">
         <v>0.025</v>
@@ -2849,7 +2855,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C7" s="40" t="n">
         <f aca="false">C5*C6</f>
@@ -2872,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I7" s="40" t="n">
         <f aca="false">G5*(1+I6)/(I5-I6)</f>
@@ -2881,7 +2887,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H8" s="0" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="I8" s="40" t="n">
         <f aca="false">I7*G6</f>
@@ -2890,7 +2896,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H9" s="0" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I9" s="40" t="n">
         <f aca="false">SUM(C7:G7)</f>
@@ -2899,7 +2905,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H10" s="0" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I10" s="41" t="n">
         <f aca="false">I8+I9</f>
@@ -2908,7 +2914,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H11" s="0" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I11" s="42" t="n">
         <v>0</v>
@@ -2916,7 +2922,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H12" s="0" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="I12" s="41" t="n">
         <f aca="false">I10-I11</f>
@@ -2925,7 +2931,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H13" s="0" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I13" s="42" t="n">
         <v>1</v>
@@ -2933,11 +2939,20 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H14" s="0" t="s">
-        <v>305</v>
-      </c>
-      <c r="I14" s="41" t="n">
-        <f aca="false">I12/I13</f>
-        <v>0</v>
+        <v>306</v>
+      </c>
+      <c r="I14" s="41" t="str">
+        <f aca="false">IF(OR(IS!E5="",IS!E5=0),"n/a - no forecast base",I12/I13)</f>
+        <v>n/a - no forecast base</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H15" s="0" t="s">
+        <v>307</v>
+      </c>
+      <c r="I15" s="2" t="str">
+        <f aca="false">IF(OR(IS!E5="",IS!E5=0),"MISSING - the DCF cannot value anything","present")</f>
+        <v>MISSING - the DCF cannot value anything</v>
       </c>
     </row>
   </sheetData>
@@ -2966,36 +2981,36 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15"/>
       <c r="B4" s="15" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
-        <v>314</v>
+      <c r="B5" s="4" t="s">
+        <v>316</v>
       </c>
       <c r="C5" s="43" t="n">
         <v>0</v>
@@ -3017,8 +3032,8 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="3" t="s">
-        <v>314</v>
+      <c r="B6" s="4" t="s">
+        <v>316</v>
       </c>
       <c r="C6" s="43" t="n">
         <v>0</v>
@@ -3040,8 +3055,8 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="3" t="s">
-        <v>314</v>
+      <c r="B7" s="4" t="s">
+        <v>316</v>
       </c>
       <c r="C7" s="43" t="n">
         <v>0</v>
@@ -3063,8 +3078,8 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="3" t="s">
-        <v>314</v>
+      <c r="B8" s="4" t="s">
+        <v>316</v>
       </c>
       <c r="C8" s="43" t="n">
         <v>0</v>
@@ -3086,8 +3101,8 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="3" t="s">
-        <v>314</v>
+      <c r="B9" s="4" t="s">
+        <v>316</v>
       </c>
       <c r="C9" s="43" t="n">
         <v>0</v>
@@ -3109,8 +3124,8 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="3" t="s">
-        <v>314</v>
+      <c r="B10" s="4" t="s">
+        <v>316</v>
       </c>
       <c r="C10" s="43" t="n">
         <v>0</v>
@@ -3132,8 +3147,8 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="3" t="s">
-        <v>314</v>
+      <c r="B11" s="4" t="s">
+        <v>316</v>
       </c>
       <c r="C11" s="43" t="n">
         <v>0</v>
@@ -3156,7 +3171,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C13" s="41" t="n">
         <f aca="false">MEDIAN(C5:C12)</f>
@@ -3209,12 +3224,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="28" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C4" s="46" t="n">
         <v>0.015</v>
@@ -3237,19 +3252,19 @@
         <v>0.08</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3257,19 +3272,19 @@
         <v>0.09</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G6" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3277,19 +3292,19 @@
         <v>0.1</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F7" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G7" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3297,19 +3312,19 @@
         <v>0.11</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3317,19 +3332,19 @@
         <v>0.12</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -3360,42 +3375,42 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15"/>
       <c r="B4" s="15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="32" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F5" s="32" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3489,7 +3504,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
@@ -3498,10 +3513,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
@@ -3509,10 +3524,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
@@ -3520,10 +3535,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
@@ -3531,10 +3546,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
@@ -3542,10 +3557,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
@@ -3553,10 +3568,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
@@ -3564,10 +3579,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
@@ -3575,7 +3590,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
@@ -3584,19 +3599,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3604,10 +3619,10 @@
         <v>1</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3615,10 +3630,10 @@
         <v>2</v>
       </c>
       <c r="C15" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="14" t="s">
         <v>43</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3626,10 +3641,10 @@
         <v>3</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3637,10 +3652,10 @@
         <v>4</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3648,15 +3663,15 @@
         <v>5</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -3665,19 +3680,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3685,10 +3700,10 @@
         <v>1</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3696,10 +3711,10 @@
         <v>2</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3707,10 +3722,10 @@
         <v>3</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3718,10 +3733,10 @@
         <v>4</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3729,15 +3744,15 @@
         <v>5</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
@@ -3746,19 +3761,19 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3766,10 +3781,10 @@
         <v>1</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3777,10 +3792,10 @@
         <v>2</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3788,10 +3803,10 @@
         <v>3</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3799,10 +3814,10 @@
         <v>4</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3810,15 +3825,15 @@
         <v>5</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
@@ -3827,19 +3842,19 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3847,10 +3862,10 @@
         <v>1</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3858,10 +3873,10 @@
         <v>2</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3869,10 +3884,10 @@
         <v>3</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3880,10 +3895,10 @@
         <v>4</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3891,15 +3906,15 @@
         <v>5</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C44" s="12"/>
       <c r="D44" s="12"/>
@@ -3908,19 +3923,19 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3928,10 +3943,10 @@
         <v>1</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3939,10 +3954,10 @@
         <v>2</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F47" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3950,10 +3965,10 @@
         <v>3</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3961,10 +3976,10 @@
         <v>4</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3972,15 +3987,15 @@
         <v>5</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C52" s="12"/>
       <c r="D52" s="12"/>
@@ -3989,19 +4004,19 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4009,10 +4024,10 @@
         <v>1</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4020,10 +4035,10 @@
         <v>2</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4031,10 +4046,10 @@
         <v>3</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4042,10 +4057,10 @@
         <v>4</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4053,15 +4068,15 @@
         <v>5</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C60" s="12"/>
       <c r="D60" s="12"/>
@@ -4070,47 +4085,47 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="C63" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="D63" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="E63" s="0" t="s">
         <v>87</v>
-      </c>
-      <c r="C63" s="0" t="s">
-        <v>88</v>
-      </c>
-      <c r="D63" s="0" t="s">
-        <v>89</v>
-      </c>
-      <c r="E63" s="0" t="s">
-        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -4187,7 +4202,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
@@ -4199,68 +4214,68 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D5" s="0" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D6" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D7" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D8" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D9" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4443,7 +4458,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
@@ -4456,87 +4471,87 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="J6" s="14" t="s">
         <v>110</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>111</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>112</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4671,36 +4686,36 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15"/>
       <c r="B4" s="15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C5" s="16" t="n">
         <v>0</v>
@@ -4718,35 +4733,35 @@
         <v>0</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="17" t="s">
         <v>129</v>
-      </c>
-      <c r="C6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="17" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C7" s="16" t="n">
         <v>0</v>
@@ -4764,12 +4779,12 @@
         <v>0</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C8" s="16" t="n">
         <v>0</v>
@@ -4787,12 +4802,12 @@
         <v>0</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C9" s="18" t="n">
         <v>0</v>
@@ -4810,12 +4825,12 @@
         <v>0</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C10" s="18" t="n">
         <v>0</v>
@@ -4833,12 +4848,12 @@
         <v>0</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C11" s="18" t="n">
         <v>0</v>
@@ -4856,12 +4871,12 @@
         <v>0</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C12" s="19" t="n">
         <f aca="false">'Cap Table &amp; Dilution'!E19</f>
@@ -4884,12 +4899,12 @@
         <v>197.35</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C13" s="16" t="n">
         <v>0</v>
@@ -4907,12 +4922,12 @@
         <v>0</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C14" s="16" t="n">
         <v>0</v>
@@ -4930,7 +4945,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -4960,37 +4975,37 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C4" s="15" t="s">
-        <v>140</v>
-      </c>
       <c r="D4" s="15" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C5" s="21" t="n">
         <v>179.7</v>
@@ -5003,12 +5018,12 @@
         <v>179.7</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" s="21" t="n">
         <v>5</v>
@@ -5021,12 +5036,12 @@
         <v>5</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C7" s="21" t="n">
         <v>2.65</v>
@@ -5039,12 +5054,12 @@
         <v>2.65</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C8" s="21" t="n">
         <v>0</v>
@@ -5057,12 +5072,12 @@
         <v>0</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C9" s="23" t="n">
         <v>100</v>
@@ -5075,12 +5090,12 @@
         <v>100</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C10" s="25" t="n">
         <v>10</v>
@@ -5093,12 +5108,12 @@
         <v>10</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C11" s="25" t="n">
         <v>767</v>
@@ -5111,12 +5126,12 @@
         <v>767</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C12" s="23" t="n">
         <v>40.6</v>
@@ -5129,12 +5144,12 @@
         <v>40.6</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="0" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C13" s="16" t="n">
         <v>0.35</v>
@@ -5147,12 +5162,12 @@
         <v>0.35</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="0" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C14" s="16" t="n">
         <v>0.1</v>
@@ -5165,17 +5180,17 @@
         <v>0.1</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="28" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="0" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C18" s="22" t="n">
         <f aca="false">IFERROR(C9/C10,0)</f>
@@ -5192,7 +5207,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="0" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C19" s="22" t="n">
         <f aca="false">SUM(C5:C8)+C18</f>
@@ -5209,7 +5224,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="0" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C20" s="27" t="n">
         <f aca="false">IFERROR(C5/C19,0)</f>
@@ -5226,7 +5241,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="0" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C21" s="27" t="n">
         <f aca="false">1-C20</f>
@@ -5243,7 +5258,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="0" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C22" s="27" t="n">
         <f aca="false">IFERROR(C6/C19,0)</f>
@@ -5260,7 +5275,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="0" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C23" s="24" t="n">
         <f aca="false">C7*C11</f>
@@ -5277,7 +5292,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="0" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C24" s="24" t="n">
         <f aca="false">C23-C12</f>
@@ -5294,7 +5309,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="0" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C25" s="22" t="n">
         <f aca="false">C19-C5-C6-C7-C8-C18</f>
@@ -5311,7 +5326,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="29" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -5341,26 +5356,26 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C4" s="15" t="s">
-        <v>140</v>
-      </c>
       <c r="D4" s="15" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C5" s="22" t="n">
         <f aca="false">'Cap Table &amp; Dilution'!C5</f>
@@ -5371,12 +5386,12 @@
         <v>100</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C6" s="22" t="n">
         <f aca="false">'Cap Table &amp; Dilution'!C8</f>
@@ -5387,12 +5402,12 @@
         <v>100</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C7" s="25" t="n">
         <v>767</v>
@@ -5401,12 +5416,12 @@
         <v>10</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C8" s="25" t="n">
         <v>767</v>
@@ -5415,12 +5430,12 @@
         <v>3</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C9" s="16" t="n">
         <v>1</v>
@@ -5429,12 +5444,12 @@
         <v>1</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C10" s="16" t="n">
         <v>0.01176</v>
@@ -5443,12 +5458,12 @@
         <v>0.08</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="0" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C13" s="24" t="n">
         <f aca="false">IFERROR((C5*C7+C6*C8)/(C5+C6),0)</f>
@@ -5461,7 +5476,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="0" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C14" s="24" t="n">
         <f aca="false">C7-C13</f>
@@ -5474,7 +5489,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="0" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C15" s="27" t="n">
         <f aca="false">IFERROR(1-C8/C7,0)</f>
@@ -5487,7 +5502,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C16" s="22" t="n">
         <f aca="false">C6*C9</f>
@@ -5500,7 +5515,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="0" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C17" s="24" t="n">
         <f aca="false">C16*C8</f>
@@ -5513,7 +5528,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="0" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C18" s="24" t="n">
         <f aca="false">(C6-C16)*C8*C10</f>
@@ -5526,7 +5541,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="0" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C19" s="24" t="n">
         <f aca="false">C17-C18</f>
@@ -5539,7 +5554,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="29" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -5569,26 +5584,26 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C4" s="15" t="s">
-        <v>140</v>
-      </c>
       <c r="D4" s="15" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C5" s="24" t="n">
         <f aca="false">'Cap Table &amp; Dilution'!C9</f>
@@ -5599,12 +5614,12 @@
         <v>500</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C6" s="26" t="n">
         <f aca="false">'Cap Table &amp; Dilution'!C10</f>
@@ -5615,12 +5630,12 @@
         <v>5</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C7" s="25" t="n">
         <v>12</v>
@@ -5629,12 +5644,12 @@
         <v>4</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C8" s="16" t="n">
         <v>0.04</v>
@@ -5643,12 +5658,12 @@
         <v>0.08</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C9" s="30" t="n">
         <v>3</v>
@@ -5657,12 +5672,12 @@
         <v>1</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C10" s="16" t="n">
         <v>0.05</v>
@@ -5671,12 +5686,12 @@
         <v>0.15</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C11" s="25" t="n">
         <v>9.5</v>
@@ -5685,12 +5700,12 @@
         <v>3.5</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C14" s="22" t="n">
         <f aca="false">IFERROR(C5/C6,0)</f>
@@ -5703,7 +5718,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="0" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C15" s="22" t="n">
         <f aca="false">IFERROR(C5/C11,0)</f>
@@ -5716,7 +5731,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C16" s="24" t="n">
         <f aca="false">C14*C7</f>
@@ -5729,7 +5744,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="0" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C17" s="24" t="n">
         <f aca="false">C5*(1+C10)</f>
@@ -5742,7 +5757,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="0" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C18" s="31" t="n">
         <f aca="false">IFERROR(C16/C5,0)</f>
@@ -5755,7 +5770,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="0" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C19" s="22" t="n">
         <f aca="false">C15-C14</f>
@@ -5768,7 +5783,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="0" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C20" s="24" t="n">
         <f aca="false">C5*C8</f>
@@ -5781,7 +5796,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="29" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -5811,26 +5826,26 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="15" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C5" s="22" t="n">
         <f aca="false">'Cap Table &amp; Dilution'!E25</f>
@@ -5841,12 +5856,12 @@
         <v>PASS</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C6" s="32" t="n">
         <f aca="false">'Cap Table &amp; Dilution'!E20+'Cap Table &amp; Dilution'!E21-1</f>
@@ -5857,12 +5872,12 @@
         <v>PASS</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C7" s="27" t="n">
         <f aca="false">'Cap Table &amp; Dilution'!E21</f>
@@ -5873,12 +5888,12 @@
         <v>PASS</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C8" s="27" t="n">
         <f aca="false">'Cap Table &amp; Dilution'!E22</f>
@@ -5889,12 +5904,12 @@
         <v>PASS</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C9" s="24" t="n">
         <f aca="false">'Cap Table &amp; Dilution'!E24</f>
@@ -5905,12 +5920,12 @@
         <v>PASS</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C10" s="32" t="n">
         <f aca="false">'Rights Offering'!C13-(('Rights Offering'!C5*'Rights Offering'!C7+'Rights Offering'!C6*'Rights Offering'!C8)/('Rights Offering'!C5+'Rights Offering'!C6))</f>
@@ -5921,12 +5936,12 @@
         <v>PASS</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C11" s="24" t="n">
         <f aca="false">'Rights Offering'!C14</f>
@@ -5937,12 +5952,12 @@
         <v>PASS</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C12" s="27" t="n">
         <f aca="false">'Rights Offering'!D9</f>
@@ -5953,12 +5968,12 @@
         <v>PASS</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="0" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C13" s="32" t="n">
         <f aca="false">'Convertible Securities'!C14-'Cap Table &amp; Dilution'!C18</f>
@@ -5969,12 +5984,12 @@
         <v>PASS</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="0" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C14" s="22" t="n">
         <f aca="false">'Convertible Securities'!D19</f>
@@ -5985,12 +6000,12 @@
         <v>REVIEW</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C16" s="33" t="str">
         <f aca="false">IF(COUNTIF(D5:D14,"FAIL")+COUNTIF(D5:D14,"BREACH")&gt;0,"BREACH",IF(COUNTIF(D5:D14,"REVIEW")&gt;0,"REVIEW","PASS"))</f>
@@ -5999,12 +6014,12 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="28" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C19" s="22" t="n">
         <f aca="false">'Cap Table &amp; Dilution'!E19</f>
@@ -6013,7 +6028,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="0" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C20" s="27" t="n">
         <f aca="false">'Cap Table &amp; Dilution'!E21</f>
@@ -6022,7 +6037,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="0" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C21" s="24" t="n">
         <f aca="false">'Cap Table &amp; Dilution'!E24</f>
@@ -6031,7 +6046,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="0" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C22" s="26" t="n">
         <f aca="false">'Rights Offering'!C13</f>
@@ -6040,7 +6055,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="0" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C23" s="24" t="n">
         <f aca="false">'Rights Offering'!C19</f>
@@ -6049,7 +6064,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C24" s="22" t="n">
         <f aca="false">'Convertible Securities'!C14</f>
@@ -6058,7 +6073,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="0" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C25" s="22" t="n">
         <f aca="false">'Convertible Securities'!D15</f>
@@ -6067,7 +6082,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C26" s="24" t="n">
         <f aca="false">'Convertible Securities'!D17</f>
